--- a/terrestrial/Level3_20-Aug-26.xlsx
+++ b/terrestrial/Level3_20-Aug-26.xlsx
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>Czechoslovakia</t>
+          <t>Czechia and Slovakia</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">

--- a/terrestrial/Level3_20-Aug-26.xlsx
+++ b/terrestrial/Level3_20-Aug-26.xlsx
@@ -4285,7 +4285,7 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>Falkland Is.</t>
+          <t>Falkland Islands (Malvinas)</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">

--- a/terrestrial/Level3_20-Aug-26.xlsx
+++ b/terrestrial/Level3_20-Aug-26.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Exchange notes</t>
+          <t>Revision notes</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">

--- a/terrestrial/Level3_20-Aug-26.xlsx
+++ b/terrestrial/Level3_20-Aug-26.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J370"/>
+  <dimension ref="A1:K370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.26953125" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="8.54296875" customWidth="1" min="8" max="8"/>
     <col width="66.81640625" customWidth="1" min="9" max="9"/>
     <col width="30.7265625" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,6 +497,11 @@
           <t>ISSUES</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n"/>
@@ -528,6 +534,7 @@
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -560,6 +567,7 @@
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -592,6 +600,7 @@
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -624,6 +633,7 @@
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -656,6 +666,7 @@
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -688,6 +699,7 @@
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -720,6 +732,7 @@
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -752,6 +765,7 @@
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -784,6 +798,7 @@
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -816,6 +831,7 @@
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -848,6 +864,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -880,6 +897,7 @@
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -908,6 +926,7 @@
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -940,6 +959,7 @@
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -972,6 +992,7 @@
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -1004,6 +1025,7 @@
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -1036,6 +1058,7 @@
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1068,6 +1091,7 @@
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -1100,6 +1124,7 @@
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -1132,6 +1157,7 @@
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -1164,6 +1190,7 @@
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -1196,6 +1223,7 @@
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -1228,6 +1256,7 @@
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -1256,6 +1285,7 @@
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -1288,6 +1318,7 @@
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -1320,6 +1351,7 @@
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -1352,6 +1384,7 @@
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -1384,6 +1417,7 @@
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -1416,6 +1450,7 @@
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -1448,6 +1483,7 @@
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -1476,6 +1512,7 @@
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -1508,6 +1545,7 @@
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -1540,6 +1578,7 @@
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -1572,6 +1611,7 @@
       <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -1600,6 +1640,7 @@
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -1632,6 +1673,7 @@
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -1664,6 +1706,7 @@
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -1692,6 +1735,7 @@
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -1724,6 +1768,7 @@
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -1756,6 +1801,7 @@
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -1788,6 +1834,7 @@
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -1820,6 +1867,7 @@
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -1852,6 +1900,7 @@
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -1884,6 +1933,7 @@
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -1916,6 +1966,7 @@
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -1948,6 +1999,7 @@
       <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -1980,6 +2032,7 @@
       <c r="H48" s="3" t="n"/>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -2012,6 +2065,7 @@
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -2044,6 +2098,7 @@
       <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -2076,6 +2131,7 @@
       <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -2108,6 +2164,7 @@
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -2140,6 +2197,7 @@
       <c r="H53" s="3" t="n"/>
       <c r="I53" s="3" t="n"/>
       <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -2172,6 +2230,7 @@
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -2204,6 +2263,7 @@
       <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -2236,6 +2296,7 @@
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n"/>
@@ -2268,6 +2329,7 @@
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
@@ -2300,6 +2362,7 @@
       <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
@@ -2332,6 +2395,7 @@
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
       <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
@@ -2372,6 +2436,7 @@
           <t>#23</t>
         </is>
       </c>
+      <c r="K60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
@@ -2412,6 +2477,7 @@
           <t>#23</t>
         </is>
       </c>
+      <c r="K61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
@@ -2452,6 +2518,7 @@
           <t>#23</t>
         </is>
       </c>
+      <c r="K62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
@@ -2484,6 +2551,7 @@
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
       <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
@@ -2524,6 +2592,7 @@
           <t>#23</t>
         </is>
       </c>
+      <c r="K64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
@@ -2556,6 +2625,7 @@
       <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
       <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -2588,6 +2658,7 @@
       <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
       <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
@@ -2620,6 +2691,7 @@
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="3" t="n"/>
       <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
@@ -2652,6 +2724,7 @@
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="n"/>
       <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n"/>
@@ -2684,6 +2757,7 @@
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
       <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
@@ -2716,6 +2790,7 @@
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="n"/>
       <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -2748,6 +2823,7 @@
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
       <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
@@ -2780,6 +2856,7 @@
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
       <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
@@ -2812,6 +2889,7 @@
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="3" t="n"/>
       <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -2844,6 +2922,7 @@
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="n"/>
       <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
@@ -2876,6 +2955,7 @@
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
       <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
@@ -2904,6 +2984,7 @@
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
       <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
@@ -2936,6 +3017,7 @@
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
       <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
@@ -2968,6 +3050,7 @@
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="n"/>
       <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
@@ -3000,6 +3083,7 @@
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
       <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
@@ -3032,6 +3116,7 @@
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
@@ -3060,6 +3145,7 @@
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="n"/>
       <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
@@ -3092,6 +3178,7 @@
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="n"/>
       <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
@@ -3124,6 +3211,7 @@
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
       <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -3152,6 +3240,7 @@
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="n"/>
       <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
@@ -3184,6 +3273,7 @@
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="n"/>
       <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
@@ -3224,6 +3314,7 @@
           <t>#30</t>
         </is>
       </c>
+      <c r="K86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n"/>
@@ -3256,6 +3347,7 @@
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="n"/>
       <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -3288,6 +3380,7 @@
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="n"/>
       <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
@@ -3320,6 +3413,7 @@
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
       <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -3352,6 +3446,7 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="n"/>
       <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -3388,6 +3483,7 @@
           <t>#20</t>
         </is>
       </c>
+      <c r="K91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -3420,6 +3516,7 @@
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
       <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n"/>
@@ -3452,6 +3549,7 @@
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
       <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -3484,6 +3582,7 @@
       <c r="H94" s="3" t="n"/>
       <c r="I94" s="3" t="n"/>
       <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -3516,6 +3615,7 @@
       <c r="H95" s="3" t="n"/>
       <c r="I95" s="3" t="n"/>
       <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -3548,6 +3648,7 @@
       <c r="H96" s="3" t="n"/>
       <c r="I96" s="3" t="n"/>
       <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
@@ -3580,6 +3681,7 @@
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>
       <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
@@ -3612,6 +3714,7 @@
       <c r="H98" s="3" t="n"/>
       <c r="I98" s="3" t="n"/>
       <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
@@ -3644,6 +3747,7 @@
       <c r="H99" s="3" t="n"/>
       <c r="I99" s="3" t="n"/>
       <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -3676,6 +3780,7 @@
       <c r="H100" s="3" t="n"/>
       <c r="I100" s="3" t="n"/>
       <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
@@ -3704,6 +3809,7 @@
       <c r="H101" s="3" t="n"/>
       <c r="I101" s="3" t="n"/>
       <c r="J101" s="3" t="n"/>
+      <c r="K101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -3736,6 +3842,7 @@
       <c r="H102" s="3" t="n"/>
       <c r="I102" s="3" t="n"/>
       <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
@@ -3768,6 +3875,7 @@
       <c r="H103" s="3" t="n"/>
       <c r="I103" s="3" t="n"/>
       <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -3800,6 +3908,7 @@
       <c r="H104" s="3" t="n"/>
       <c r="I104" s="3" t="n"/>
       <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
@@ -3844,6 +3953,7 @@
           <t>#12</t>
         </is>
       </c>
+      <c r="K105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -3876,6 +3986,7 @@
       <c r="H106" s="3" t="n"/>
       <c r="I106" s="3" t="n"/>
       <c r="J106" s="3" t="n"/>
+      <c r="K106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
@@ -3908,6 +4019,7 @@
       <c r="H107" s="3" t="n"/>
       <c r="I107" s="3" t="n"/>
       <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -3940,6 +4052,7 @@
       <c r="H108" s="3" t="n"/>
       <c r="I108" s="3" t="n"/>
       <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
@@ -3972,6 +4085,7 @@
       <c r="H109" s="3" t="n"/>
       <c r="I109" s="3" t="n"/>
       <c r="J109" s="3" t="n"/>
+      <c r="K109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
@@ -4004,6 +4118,7 @@
       <c r="H110" s="3" t="n"/>
       <c r="I110" s="3" t="n"/>
       <c r="J110" s="3" t="n"/>
+      <c r="K110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
@@ -4036,6 +4151,7 @@
       <c r="H111" s="3" t="n"/>
       <c r="I111" s="3" t="n"/>
       <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -4064,6 +4180,7 @@
       <c r="H112" s="3" t="n"/>
       <c r="I112" s="3" t="n"/>
       <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
@@ -4096,6 +4213,7 @@
       <c r="H113" s="3" t="n"/>
       <c r="I113" s="3" t="n"/>
       <c r="J113" s="3" t="n"/>
+      <c r="K113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -4128,6 +4246,7 @@
       <c r="H114" s="3" t="n"/>
       <c r="I114" s="3" t="n"/>
       <c r="J114" s="3" t="n"/>
+      <c r="K114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
@@ -4160,6 +4279,7 @@
       <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="n"/>
       <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -4192,6 +4312,7 @@
       <c r="H116" s="3" t="n"/>
       <c r="I116" s="3" t="n"/>
       <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
@@ -4224,6 +4345,7 @@
       <c r="H117" s="3" t="n"/>
       <c r="I117" s="3" t="n"/>
       <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -4256,6 +4378,7 @@
       <c r="H118" s="3" t="n"/>
       <c r="I118" s="3" t="n"/>
       <c r="J118" s="3" t="n"/>
+      <c r="K118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
@@ -4284,6 +4407,7 @@
       <c r="H119" s="3" t="n"/>
       <c r="I119" s="3" t="n"/>
       <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -4316,6 +4440,7 @@
       <c r="H120" s="3" t="n"/>
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
@@ -4348,6 +4473,7 @@
       <c r="H121" s="3" t="n"/>
       <c r="I121" s="3" t="n"/>
       <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -4380,6 +4506,7 @@
       <c r="H122" s="3" t="n"/>
       <c r="I122" s="3" t="n"/>
       <c r="J122" s="3" t="n"/>
+      <c r="K122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
@@ -4412,6 +4539,7 @@
       <c r="H123" s="3" t="n"/>
       <c r="I123" s="3" t="n"/>
       <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -4444,6 +4572,7 @@
       <c r="H124" s="3" t="n"/>
       <c r="I124" s="3" t="n"/>
       <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
@@ -4476,6 +4605,7 @@
       <c r="H125" s="3" t="n"/>
       <c r="I125" s="3" t="n"/>
       <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -4504,6 +4634,7 @@
       <c r="H126" s="3" t="n"/>
       <c r="I126" s="3" t="n"/>
       <c r="J126" s="3" t="n"/>
+      <c r="K126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -4536,6 +4667,7 @@
       <c r="H127" s="3" t="n"/>
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="3" t="n"/>
+      <c r="K127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -4568,6 +4700,7 @@
       <c r="H128" s="3" t="n"/>
       <c r="I128" s="3" t="n"/>
       <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
@@ -4600,6 +4733,7 @@
       <c r="H129" s="3" t="n"/>
       <c r="I129" s="3" t="n"/>
       <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -4628,6 +4762,7 @@
       <c r="H130" s="3" t="n"/>
       <c r="I130" s="3" t="n"/>
       <c r="J130" s="3" t="n"/>
+      <c r="K130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
@@ -4656,6 +4791,7 @@
       <c r="H131" s="3" t="n"/>
       <c r="I131" s="3" t="n"/>
       <c r="J131" s="3" t="n"/>
+      <c r="K131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -4688,6 +4824,7 @@
       <c r="H132" s="3" t="n"/>
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="n"/>
+      <c r="K132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
@@ -4720,6 +4857,7 @@
       <c r="H133" s="3" t="n"/>
       <c r="I133" s="3" t="n"/>
       <c r="J133" s="3" t="n"/>
+      <c r="K133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -4752,6 +4890,7 @@
       <c r="H134" s="3" t="n"/>
       <c r="I134" s="3" t="n"/>
       <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
@@ -4784,6 +4923,7 @@
       <c r="H135" s="3" t="n"/>
       <c r="I135" s="3" t="n"/>
       <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
@@ -4816,6 +4956,7 @@
       <c r="H136" s="3" t="n"/>
       <c r="I136" s="3" t="n"/>
       <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
@@ -4848,6 +4989,7 @@
       <c r="H137" s="3" t="n"/>
       <c r="I137" s="3" t="n"/>
       <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
@@ -4880,6 +5022,7 @@
       <c r="H138" s="3" t="n"/>
       <c r="I138" s="3" t="n"/>
       <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
@@ -4912,6 +5055,7 @@
       <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="n"/>
       <c r="J139" s="3" t="n"/>
+      <c r="K139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -4944,6 +5088,7 @@
       <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="n"/>
+      <c r="K140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
@@ -4976,6 +5121,7 @@
       <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -5004,6 +5150,7 @@
       <c r="H142" s="3" t="n"/>
       <c r="I142" s="3" t="n"/>
       <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
@@ -5036,6 +5183,7 @@
       <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="n"/>
       <c r="J143" s="3" t="n"/>
+      <c r="K143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -5068,6 +5216,7 @@
       <c r="H144" s="3" t="n"/>
       <c r="I144" s="3" t="n"/>
       <c r="J144" s="3" t="n"/>
+      <c r="K144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
@@ -5100,6 +5249,7 @@
       <c r="H145" s="3" t="n"/>
       <c r="I145" s="3" t="n"/>
       <c r="J145" s="3" t="n"/>
+      <c r="K145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -5128,6 +5278,7 @@
       <c r="H146" s="3" t="n"/>
       <c r="I146" s="3" t="n"/>
       <c r="J146" s="3" t="n"/>
+      <c r="K146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
@@ -5160,6 +5311,7 @@
       <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="n"/>
       <c r="J147" s="3" t="n"/>
+      <c r="K147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -5192,6 +5344,7 @@
       <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="n"/>
       <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
@@ -5224,6 +5377,7 @@
       <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="n"/>
       <c r="J149" s="3" t="n"/>
+      <c r="K149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -5256,6 +5410,7 @@
       <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="n"/>
       <c r="J150" s="3" t="n"/>
+      <c r="K150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
@@ -5288,6 +5443,7 @@
       <c r="H151" s="3" t="n"/>
       <c r="I151" s="3" t="n"/>
       <c r="J151" s="3" t="n"/>
+      <c r="K151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -5320,6 +5476,7 @@
       <c r="H152" s="3" t="n"/>
       <c r="I152" s="3" t="n"/>
       <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n"/>
@@ -5352,6 +5509,7 @@
       <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="n"/>
       <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -5384,6 +5542,7 @@
       <c r="H154" s="3" t="n"/>
       <c r="I154" s="3" t="n"/>
       <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
@@ -5416,6 +5575,7 @@
       <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="n"/>
       <c r="J155" s="3" t="n"/>
+      <c r="K155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -5448,6 +5608,7 @@
       <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="n"/>
       <c r="J156" s="3" t="n"/>
+      <c r="K156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n"/>
@@ -5480,6 +5641,7 @@
       <c r="H157" s="3" t="n"/>
       <c r="I157" s="3" t="n"/>
       <c r="J157" s="3" t="n"/>
+      <c r="K157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
@@ -5512,6 +5674,7 @@
       <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="n"/>
       <c r="J158" s="3" t="n"/>
+      <c r="K158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n"/>
@@ -5544,6 +5707,7 @@
       <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="n"/>
       <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
@@ -5572,6 +5736,7 @@
       <c r="H160" s="3" t="n"/>
       <c r="I160" s="3" t="n"/>
       <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n"/>
@@ -5604,6 +5769,7 @@
       <c r="H161" s="3" t="n"/>
       <c r="I161" s="3" t="n"/>
       <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
@@ -5636,6 +5802,7 @@
       <c r="H162" s="3" t="n"/>
       <c r="I162" s="3" t="n"/>
       <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n"/>
@@ -5676,6 +5843,7 @@
           <t>#3</t>
         </is>
       </c>
+      <c r="K163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
@@ -5708,6 +5876,7 @@
       <c r="H164" s="3" t="n"/>
       <c r="I164" s="3" t="n"/>
       <c r="J164" s="3" t="n"/>
+      <c r="K164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n"/>
@@ -5740,6 +5909,7 @@
       <c r="H165" s="3" t="n"/>
       <c r="I165" s="3" t="n"/>
       <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
@@ -5772,6 +5942,7 @@
       <c r="H166" s="3" t="n"/>
       <c r="I166" s="3" t="n"/>
       <c r="J166" s="3" t="n"/>
+      <c r="K166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n"/>
@@ -5804,6 +5975,7 @@
       <c r="H167" s="3" t="n"/>
       <c r="I167" s="3" t="n"/>
       <c r="J167" s="3" t="n"/>
+      <c r="K167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
@@ -5836,6 +6008,7 @@
       <c r="H168" s="3" t="n"/>
       <c r="I168" s="3" t="n"/>
       <c r="J168" s="3" t="n"/>
+      <c r="K168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n"/>
@@ -5868,6 +6041,7 @@
       <c r="H169" s="3" t="n"/>
       <c r="I169" s="3" t="n"/>
       <c r="J169" s="3" t="n"/>
+      <c r="K169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n"/>
@@ -5900,6 +6074,7 @@
       <c r="H170" s="3" t="n"/>
       <c r="I170" s="3" t="n"/>
       <c r="J170" s="3" t="n"/>
+      <c r="K170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n"/>
@@ -5928,6 +6103,7 @@
       <c r="H171" s="3" t="n"/>
       <c r="I171" s="3" t="n"/>
       <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n"/>
@@ -5960,6 +6136,7 @@
       <c r="H172" s="3" t="n"/>
       <c r="I172" s="3" t="n"/>
       <c r="J172" s="3" t="n"/>
+      <c r="K172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n"/>
@@ -5992,6 +6169,7 @@
       <c r="H173" s="3" t="n"/>
       <c r="I173" s="3" t="n"/>
       <c r="J173" s="3" t="n"/>
+      <c r="K173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n"/>
@@ -6020,6 +6198,7 @@
       <c r="H174" s="3" t="n"/>
       <c r="I174" s="3" t="n"/>
       <c r="J174" s="3" t="n"/>
+      <c r="K174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n"/>
@@ -6052,6 +6231,7 @@
       <c r="H175" s="3" t="n"/>
       <c r="I175" s="3" t="n"/>
       <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n"/>
@@ -6080,6 +6260,7 @@
       <c r="H176" s="3" t="n"/>
       <c r="I176" s="3" t="n"/>
       <c r="J176" s="3" t="n"/>
+      <c r="K176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n"/>
@@ -6112,6 +6293,7 @@
       <c r="H177" s="3" t="n"/>
       <c r="I177" s="3" t="n"/>
       <c r="J177" s="3" t="n"/>
+      <c r="K177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n"/>
@@ -6140,6 +6322,7 @@
       <c r="H178" s="3" t="n"/>
       <c r="I178" s="3" t="n"/>
       <c r="J178" s="3" t="n"/>
+      <c r="K178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n"/>
@@ -6172,6 +6355,7 @@
       <c r="H179" s="3" t="n"/>
       <c r="I179" s="3" t="n"/>
       <c r="J179" s="3" t="n"/>
+      <c r="K179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n"/>
@@ -6204,6 +6388,7 @@
       <c r="H180" s="3" t="n"/>
       <c r="I180" s="3" t="n"/>
       <c r="J180" s="3" t="n"/>
+      <c r="K180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n"/>
@@ -6236,6 +6421,7 @@
       <c r="H181" s="3" t="n"/>
       <c r="I181" s="3" t="n"/>
       <c r="J181" s="3" t="n"/>
+      <c r="K181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n"/>
@@ -6268,6 +6454,7 @@
       <c r="H182" s="3" t="n"/>
       <c r="I182" s="3" t="n"/>
       <c r="J182" s="3" t="n"/>
+      <c r="K182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n"/>
@@ -6300,6 +6487,7 @@
       <c r="H183" s="3" t="n"/>
       <c r="I183" s="3" t="n"/>
       <c r="J183" s="3" t="n"/>
+      <c r="K183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n"/>
@@ -6332,6 +6520,7 @@
       <c r="H184" s="3" t="n"/>
       <c r="I184" s="3" t="n"/>
       <c r="J184" s="3" t="n"/>
+      <c r="K184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n"/>
@@ -6365,6 +6554,7 @@
         </is>
       </c>
       <c r="J185" s="3" t="n"/>
+      <c r="K185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n"/>
@@ -6397,6 +6587,7 @@
       <c r="H186" s="3" t="n"/>
       <c r="I186" s="3" t="n"/>
       <c r="J186" s="3" t="n"/>
+      <c r="K186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n"/>
@@ -6429,6 +6620,7 @@
       <c r="H187" s="3" t="n"/>
       <c r="I187" s="3" t="n"/>
       <c r="J187" s="3" t="n"/>
+      <c r="K187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n"/>
@@ -6461,6 +6653,7 @@
       <c r="H188" s="3" t="n"/>
       <c r="I188" s="3" t="n"/>
       <c r="J188" s="3" t="n"/>
+      <c r="K188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n"/>
@@ -6493,6 +6686,7 @@
       <c r="H189" s="3" t="n"/>
       <c r="I189" s="3" t="n"/>
       <c r="J189" s="3" t="n"/>
+      <c r="K189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n"/>
@@ -6525,6 +6719,7 @@
       <c r="H190" s="3" t="n"/>
       <c r="I190" s="3" t="n"/>
       <c r="J190" s="3" t="n"/>
+      <c r="K190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n"/>
@@ -6557,6 +6752,7 @@
       <c r="H191" s="3" t="n"/>
       <c r="I191" s="3" t="n"/>
       <c r="J191" s="3" t="n"/>
+      <c r="K191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n"/>
@@ -6589,6 +6785,7 @@
       <c r="H192" s="3" t="n"/>
       <c r="I192" s="3" t="n"/>
       <c r="J192" s="3" t="n"/>
+      <c r="K192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n"/>
@@ -6621,6 +6818,7 @@
       <c r="H193" s="3" t="n"/>
       <c r="I193" s="3" t="n"/>
       <c r="J193" s="3" t="n"/>
+      <c r="K193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n"/>
@@ -6649,6 +6847,7 @@
       <c r="H194" s="3" t="n"/>
       <c r="I194" s="3" t="n"/>
       <c r="J194" s="3" t="n"/>
+      <c r="K194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n"/>
@@ -6681,6 +6880,7 @@
       <c r="H195" s="3" t="n"/>
       <c r="I195" s="3" t="n"/>
       <c r="J195" s="3" t="n"/>
+      <c r="K195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n"/>
@@ -6713,6 +6913,7 @@
       <c r="H196" s="3" t="n"/>
       <c r="I196" s="3" t="n"/>
       <c r="J196" s="3" t="n"/>
+      <c r="K196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n"/>
@@ -6745,6 +6946,7 @@
       <c r="H197" s="3" t="n"/>
       <c r="I197" s="3" t="n"/>
       <c r="J197" s="3" t="n"/>
+      <c r="K197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n"/>
@@ -6773,6 +6975,7 @@
       <c r="H198" s="3" t="n"/>
       <c r="I198" s="3" t="n"/>
       <c r="J198" s="3" t="n"/>
+      <c r="K198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n"/>
@@ -6805,6 +7008,7 @@
       <c r="H199" s="3" t="n"/>
       <c r="I199" s="3" t="n"/>
       <c r="J199" s="3" t="n"/>
+      <c r="K199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n"/>
@@ -6837,6 +7041,7 @@
       <c r="H200" s="3" t="n"/>
       <c r="I200" s="3" t="n"/>
       <c r="J200" s="3" t="n"/>
+      <c r="K200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n"/>
@@ -6865,6 +7070,7 @@
       <c r="H201" s="3" t="n"/>
       <c r="I201" s="3" t="n"/>
       <c r="J201" s="3" t="n"/>
+      <c r="K201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n"/>
@@ -6897,6 +7103,7 @@
       <c r="H202" s="3" t="n"/>
       <c r="I202" s="3" t="n"/>
       <c r="J202" s="3" t="n"/>
+      <c r="K202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n"/>
@@ -6929,6 +7136,7 @@
       <c r="H203" s="3" t="n"/>
       <c r="I203" s="3" t="n"/>
       <c r="J203" s="3" t="n"/>
+      <c r="K203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n"/>
@@ -6961,6 +7169,7 @@
       <c r="H204" s="3" t="n"/>
       <c r="I204" s="3" t="n"/>
       <c r="J204" s="3" t="n"/>
+      <c r="K204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n"/>
@@ -6993,6 +7202,7 @@
       <c r="H205" s="3" t="n"/>
       <c r="I205" s="3" t="n"/>
       <c r="J205" s="3" t="n"/>
+      <c r="K205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n"/>
@@ -7025,6 +7235,7 @@
       <c r="H206" s="3" t="n"/>
       <c r="I206" s="3" t="n"/>
       <c r="J206" s="3" t="n"/>
+      <c r="K206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n"/>
@@ -7057,6 +7268,7 @@
       <c r="H207" s="3" t="n"/>
       <c r="I207" s="3" t="n"/>
       <c r="J207" s="3" t="n"/>
+      <c r="K207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n"/>
@@ -7089,6 +7301,7 @@
       <c r="H208" s="3" t="n"/>
       <c r="I208" s="3" t="n"/>
       <c r="J208" s="3" t="n"/>
+      <c r="K208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n"/>
@@ -7121,6 +7334,7 @@
       <c r="H209" s="3" t="n"/>
       <c r="I209" s="3" t="n"/>
       <c r="J209" s="3" t="n"/>
+      <c r="K209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n"/>
@@ -7153,6 +7367,7 @@
       <c r="H210" s="3" t="n"/>
       <c r="I210" s="3" t="n"/>
       <c r="J210" s="3" t="n"/>
+      <c r="K210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n"/>
@@ -7185,6 +7400,7 @@
       <c r="H211" s="3" t="n"/>
       <c r="I211" s="3" t="n"/>
       <c r="J211" s="3" t="n"/>
+      <c r="K211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n"/>
@@ -7217,6 +7433,7 @@
       <c r="H212" s="3" t="n"/>
       <c r="I212" s="3" t="n"/>
       <c r="J212" s="3" t="n"/>
+      <c r="K212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n"/>
@@ -7249,6 +7466,7 @@
       <c r="H213" s="3" t="n"/>
       <c r="I213" s="3" t="n"/>
       <c r="J213" s="3" t="n"/>
+      <c r="K213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n"/>
@@ -7281,6 +7499,7 @@
       <c r="H214" s="3" t="n"/>
       <c r="I214" s="3" t="n"/>
       <c r="J214" s="3" t="n"/>
+      <c r="K214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n"/>
@@ -7313,6 +7532,7 @@
       <c r="H215" s="3" t="n"/>
       <c r="I215" s="3" t="n"/>
       <c r="J215" s="3" t="n"/>
+      <c r="K215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n"/>
@@ -7345,6 +7565,7 @@
       <c r="H216" s="3" t="n"/>
       <c r="I216" s="3" t="n"/>
       <c r="J216" s="3" t="n"/>
+      <c r="K216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="n"/>
@@ -7377,6 +7598,7 @@
       <c r="H217" s="3" t="n"/>
       <c r="I217" s="3" t="n"/>
       <c r="J217" s="3" t="n"/>
+      <c r="K217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n"/>
@@ -7409,6 +7631,7 @@
       <c r="H218" s="3" t="n"/>
       <c r="I218" s="3" t="n"/>
       <c r="J218" s="3" t="n"/>
+      <c r="K218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n"/>
@@ -7441,6 +7664,7 @@
       <c r="H219" s="3" t="n"/>
       <c r="I219" s="3" t="n"/>
       <c r="J219" s="3" t="n"/>
+      <c r="K219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n"/>
@@ -7473,6 +7697,7 @@
       <c r="H220" s="3" t="n"/>
       <c r="I220" s="3" t="n"/>
       <c r="J220" s="3" t="n"/>
+      <c r="K220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n"/>
@@ -7505,6 +7730,7 @@
       <c r="H221" s="3" t="n"/>
       <c r="I221" s="3" t="n"/>
       <c r="J221" s="3" t="n"/>
+      <c r="K221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n"/>
@@ -7537,6 +7763,7 @@
       <c r="H222" s="3" t="n"/>
       <c r="I222" s="3" t="n"/>
       <c r="J222" s="3" t="n"/>
+      <c r="K222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="n"/>
@@ -7569,6 +7796,7 @@
       <c r="H223" s="3" t="n"/>
       <c r="I223" s="3" t="n"/>
       <c r="J223" s="3" t="n"/>
+      <c r="K223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n"/>
@@ -7601,6 +7829,7 @@
       <c r="H224" s="3" t="n"/>
       <c r="I224" s="3" t="n"/>
       <c r="J224" s="3" t="n"/>
+      <c r="K224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n"/>
@@ -7633,6 +7862,7 @@
       <c r="H225" s="3" t="n"/>
       <c r="I225" s="3" t="n"/>
       <c r="J225" s="3" t="n"/>
+      <c r="K225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n"/>
@@ -7665,6 +7895,7 @@
       <c r="H226" s="3" t="n"/>
       <c r="I226" s="3" t="n"/>
       <c r="J226" s="3" t="n"/>
+      <c r="K226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n"/>
@@ -7693,6 +7924,7 @@
       <c r="H227" s="3" t="n"/>
       <c r="I227" s="3" t="n"/>
       <c r="J227" s="3" t="n"/>
+      <c r="K227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n"/>
@@ -7721,6 +7953,7 @@
       <c r="H228" s="3" t="n"/>
       <c r="I228" s="3" t="n"/>
       <c r="J228" s="3" t="n"/>
+      <c r="K228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n"/>
@@ -7753,6 +7986,7 @@
       <c r="H229" s="3" t="n"/>
       <c r="I229" s="3" t="n"/>
       <c r="J229" s="3" t="n"/>
+      <c r="K229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n"/>
@@ -7785,6 +8019,7 @@
       <c r="H230" s="3" t="n"/>
       <c r="I230" s="3" t="n"/>
       <c r="J230" s="3" t="n"/>
+      <c r="K230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n"/>
@@ -7817,6 +8052,7 @@
       <c r="H231" s="3" t="n"/>
       <c r="I231" s="3" t="n"/>
       <c r="J231" s="3" t="n"/>
+      <c r="K231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n"/>
@@ -7849,6 +8085,7 @@
         </is>
       </c>
       <c r="J232" s="3" t="n"/>
+      <c r="K232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="n"/>
@@ -7881,6 +8118,7 @@
       <c r="H233" s="3" t="n"/>
       <c r="I233" s="3" t="n"/>
       <c r="J233" s="3" t="n"/>
+      <c r="K233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n"/>
@@ -7913,6 +8151,7 @@
       <c r="H234" s="3" t="n"/>
       <c r="I234" s="3" t="n"/>
       <c r="J234" s="3" t="n"/>
+      <c r="K234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="n"/>
@@ -7945,6 +8184,7 @@
       <c r="H235" s="3" t="n"/>
       <c r="I235" s="3" t="n"/>
       <c r="J235" s="3" t="n"/>
+      <c r="K235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n"/>
@@ -7977,6 +8217,7 @@
       <c r="H236" s="3" t="n"/>
       <c r="I236" s="3" t="n"/>
       <c r="J236" s="3" t="n"/>
+      <c r="K236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n"/>
@@ -8009,6 +8250,7 @@
       <c r="H237" s="3" t="n"/>
       <c r="I237" s="3" t="n"/>
       <c r="J237" s="3" t="n"/>
+      <c r="K237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n"/>
@@ -8041,6 +8283,7 @@
       <c r="H238" s="3" t="n"/>
       <c r="I238" s="3" t="n"/>
       <c r="J238" s="3" t="n"/>
+      <c r="K238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n"/>
@@ -8073,6 +8316,7 @@
       <c r="H239" s="3" t="n"/>
       <c r="I239" s="3" t="n"/>
       <c r="J239" s="3" t="n"/>
+      <c r="K239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n"/>
@@ -8105,6 +8349,7 @@
       <c r="H240" s="3" t="n"/>
       <c r="I240" s="3" t="n"/>
       <c r="J240" s="3" t="n"/>
+      <c r="K240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="n"/>
@@ -8137,6 +8382,7 @@
       <c r="H241" s="3" t="n"/>
       <c r="I241" s="3" t="n"/>
       <c r="J241" s="3" t="n"/>
+      <c r="K241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -8181,6 +8427,7 @@
           <t>#2</t>
         </is>
       </c>
+      <c r="K242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="n"/>
@@ -8213,6 +8460,7 @@
       <c r="H243" s="3" t="n"/>
       <c r="I243" s="3" t="n"/>
       <c r="J243" s="3" t="n"/>
+      <c r="K243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="n"/>
@@ -8241,6 +8489,7 @@
       <c r="H244" s="3" t="n"/>
       <c r="I244" s="3" t="n"/>
       <c r="J244" s="3" t="n"/>
+      <c r="K244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="n"/>
@@ -8273,6 +8522,7 @@
       <c r="H245" s="3" t="n"/>
       <c r="I245" s="3" t="n"/>
       <c r="J245" s="3" t="n"/>
+      <c r="K245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="n"/>
@@ -8305,6 +8555,7 @@
       <c r="H246" s="3" t="n"/>
       <c r="I246" s="3" t="n"/>
       <c r="J246" s="3" t="n"/>
+      <c r="K246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="n"/>
@@ -8337,6 +8588,7 @@
       <c r="H247" s="3" t="n"/>
       <c r="I247" s="3" t="n"/>
       <c r="J247" s="3" t="n"/>
+      <c r="K247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="n"/>
@@ -8369,6 +8621,7 @@
       <c r="H248" s="3" t="n"/>
       <c r="I248" s="3" t="n"/>
       <c r="J248" s="3" t="n"/>
+      <c r="K248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="n"/>
@@ -8401,6 +8654,7 @@
       <c r="H249" s="3" t="n"/>
       <c r="I249" s="3" t="n"/>
       <c r="J249" s="3" t="n"/>
+      <c r="K249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="n"/>
@@ -8433,6 +8687,7 @@
       <c r="H250" s="3" t="n"/>
       <c r="I250" s="3" t="n"/>
       <c r="J250" s="3" t="n"/>
+      <c r="K250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="n"/>
@@ -8465,6 +8720,7 @@
       <c r="H251" s="3" t="n"/>
       <c r="I251" s="3" t="n"/>
       <c r="J251" s="3" t="n"/>
+      <c r="K251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="n"/>
@@ -8497,6 +8753,7 @@
       <c r="H252" s="3" t="n"/>
       <c r="I252" s="3" t="n"/>
       <c r="J252" s="3" t="n"/>
+      <c r="K252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="n"/>
@@ -8529,6 +8786,7 @@
       <c r="H253" s="3" t="n"/>
       <c r="I253" s="3" t="n"/>
       <c r="J253" s="3" t="n"/>
+      <c r="K253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n"/>
@@ -8561,6 +8819,7 @@
       <c r="H254" s="3" t="n"/>
       <c r="I254" s="3" t="n"/>
       <c r="J254" s="3" t="n"/>
+      <c r="K254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="n"/>
@@ -8593,6 +8852,7 @@
       <c r="H255" s="3" t="n"/>
       <c r="I255" s="3" t="n"/>
       <c r="J255" s="3" t="n"/>
+      <c r="K255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="n"/>
@@ -8625,6 +8885,7 @@
       <c r="H256" s="3" t="n"/>
       <c r="I256" s="3" t="n"/>
       <c r="J256" s="3" t="n"/>
+      <c r="K256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="n"/>
@@ -8657,6 +8918,7 @@
       <c r="H257" s="3" t="n"/>
       <c r="I257" s="3" t="n"/>
       <c r="J257" s="3" t="n"/>
+      <c r="K257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="n"/>
@@ -8689,6 +8951,7 @@
       <c r="H258" s="3" t="n"/>
       <c r="I258" s="3" t="n"/>
       <c r="J258" s="3" t="n"/>
+      <c r="K258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="n"/>
@@ -8721,6 +8984,7 @@
       <c r="H259" s="3" t="n"/>
       <c r="I259" s="3" t="n"/>
       <c r="J259" s="3" t="n"/>
+      <c r="K259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="n"/>
@@ -8749,6 +9013,7 @@
       <c r="H260" s="3" t="n"/>
       <c r="I260" s="3" t="n"/>
       <c r="J260" s="3" t="n"/>
+      <c r="K260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="n"/>
@@ -8781,6 +9046,7 @@
       <c r="H261" s="3" t="n"/>
       <c r="I261" s="3" t="n"/>
       <c r="J261" s="3" t="n"/>
+      <c r="K261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="n"/>
@@ -8813,6 +9079,7 @@
       <c r="H262" s="3" t="n"/>
       <c r="I262" s="3" t="n"/>
       <c r="J262" s="3" t="n"/>
+      <c r="K262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="n"/>
@@ -8845,6 +9112,7 @@
       <c r="H263" s="3" t="n"/>
       <c r="I263" s="3" t="n"/>
       <c r="J263" s="3" t="n"/>
+      <c r="K263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n"/>
@@ -8877,6 +9145,7 @@
       <c r="H264" s="3" t="n"/>
       <c r="I264" s="3" t="n"/>
       <c r="J264" s="3" t="n"/>
+      <c r="K264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="n"/>
@@ -8909,6 +9178,7 @@
       <c r="H265" s="3" t="n"/>
       <c r="I265" s="3" t="n"/>
       <c r="J265" s="3" t="n"/>
+      <c r="K265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="n"/>
@@ -8941,6 +9211,7 @@
       <c r="H266" s="3" t="n"/>
       <c r="I266" s="3" t="n"/>
       <c r="J266" s="3" t="n"/>
+      <c r="K266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="n"/>
@@ -8973,6 +9244,7 @@
       <c r="H267" s="3" t="n"/>
       <c r="I267" s="3" t="n"/>
       <c r="J267" s="3" t="n"/>
+      <c r="K267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="n"/>
@@ -9005,6 +9277,7 @@
       <c r="H268" s="3" t="n"/>
       <c r="I268" s="3" t="n"/>
       <c r="J268" s="3" t="n"/>
+      <c r="K268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="n"/>
@@ -9037,6 +9310,7 @@
       <c r="H269" s="3" t="n"/>
       <c r="I269" s="3" t="n"/>
       <c r="J269" s="3" t="n"/>
+      <c r="K269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="n"/>
@@ -9069,6 +9343,7 @@
       <c r="H270" s="3" t="n"/>
       <c r="I270" s="3" t="n"/>
       <c r="J270" s="3" t="n"/>
+      <c r="K270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="n"/>
@@ -9101,6 +9376,7 @@
       <c r="H271" s="3" t="n"/>
       <c r="I271" s="3" t="n"/>
       <c r="J271" s="3" t="n"/>
+      <c r="K271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="n"/>
@@ -9133,6 +9409,7 @@
       <c r="H272" s="3" t="n"/>
       <c r="I272" s="3" t="n"/>
       <c r="J272" s="3" t="n"/>
+      <c r="K272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="n"/>
@@ -9165,6 +9442,7 @@
       <c r="H273" s="3" t="n"/>
       <c r="I273" s="3" t="n"/>
       <c r="J273" s="3" t="n"/>
+      <c r="K273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="n"/>
@@ -9197,6 +9475,7 @@
       <c r="H274" s="3" t="n"/>
       <c r="I274" s="3" t="n"/>
       <c r="J274" s="3" t="n"/>
+      <c r="K274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="n"/>
@@ -9229,6 +9508,7 @@
       <c r="H275" s="3" t="n"/>
       <c r="I275" s="3" t="n"/>
       <c r="J275" s="3" t="n"/>
+      <c r="K275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n"/>
@@ -9261,6 +9541,7 @@
       <c r="H276" s="3" t="n"/>
       <c r="I276" s="3" t="n"/>
       <c r="J276" s="3" t="n"/>
+      <c r="K276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="n"/>
@@ -9293,6 +9574,7 @@
       <c r="H277" s="3" t="n"/>
       <c r="I277" s="3" t="n"/>
       <c r="J277" s="3" t="n"/>
+      <c r="K277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n"/>
@@ -9325,6 +9607,7 @@
       <c r="H278" s="3" t="n"/>
       <c r="I278" s="3" t="n"/>
       <c r="J278" s="3" t="n"/>
+      <c r="K278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="n"/>
@@ -9357,6 +9640,7 @@
       <c r="H279" s="3" t="n"/>
       <c r="I279" s="3" t="n"/>
       <c r="J279" s="3" t="n"/>
+      <c r="K279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="n"/>
@@ -9389,6 +9673,7 @@
       <c r="H280" s="3" t="n"/>
       <c r="I280" s="3" t="n"/>
       <c r="J280" s="3" t="n"/>
+      <c r="K280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="n"/>
@@ -9421,6 +9706,7 @@
       <c r="H281" s="3" t="n"/>
       <c r="I281" s="3" t="n"/>
       <c r="J281" s="3" t="n"/>
+      <c r="K281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="n"/>
@@ -9453,6 +9739,7 @@
       <c r="H282" s="3" t="n"/>
       <c r="I282" s="3" t="n"/>
       <c r="J282" s="3" t="n"/>
+      <c r="K282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="n"/>
@@ -9485,6 +9772,7 @@
       <c r="H283" s="3" t="n"/>
       <c r="I283" s="3" t="n"/>
       <c r="J283" s="3" t="n"/>
+      <c r="K283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="n"/>
@@ -9517,6 +9805,7 @@
       <c r="H284" s="3" t="n"/>
       <c r="I284" s="3" t="n"/>
       <c r="J284" s="3" t="n"/>
+      <c r="K284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="n"/>
@@ -9549,6 +9838,7 @@
       <c r="H285" s="3" t="n"/>
       <c r="I285" s="3" t="n"/>
       <c r="J285" s="3" t="n"/>
+      <c r="K285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="n"/>
@@ -9577,6 +9867,7 @@
       <c r="H286" s="3" t="n"/>
       <c r="I286" s="3" t="n"/>
       <c r="J286" s="3" t="n"/>
+      <c r="K286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="n"/>
@@ -9609,6 +9900,7 @@
       <c r="H287" s="3" t="n"/>
       <c r="I287" s="3" t="n"/>
       <c r="J287" s="3" t="n"/>
+      <c r="K287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="n"/>
@@ -9641,6 +9933,7 @@
       <c r="H288" s="3" t="n"/>
       <c r="I288" s="3" t="n"/>
       <c r="J288" s="3" t="n"/>
+      <c r="K288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="n"/>
@@ -9673,6 +9966,7 @@
       <c r="H289" s="3" t="n"/>
       <c r="I289" s="3" t="n"/>
       <c r="J289" s="3" t="n"/>
+      <c r="K289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="n"/>
@@ -9705,6 +9999,7 @@
       <c r="H290" s="3" t="n"/>
       <c r="I290" s="3" t="n"/>
       <c r="J290" s="3" t="n"/>
+      <c r="K290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="n"/>
@@ -9737,6 +10032,7 @@
       <c r="H291" s="3" t="n"/>
       <c r="I291" s="3" t="n"/>
       <c r="J291" s="3" t="n"/>
+      <c r="K291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="n"/>
@@ -9765,6 +10061,7 @@
       <c r="H292" s="3" t="n"/>
       <c r="I292" s="3" t="n"/>
       <c r="J292" s="3" t="n"/>
+      <c r="K292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n"/>
@@ -9797,6 +10094,7 @@
       <c r="H293" s="3" t="n"/>
       <c r="I293" s="3" t="n"/>
       <c r="J293" s="3" t="n"/>
+      <c r="K293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="n"/>
@@ -9829,6 +10127,7 @@
       <c r="H294" s="3" t="n"/>
       <c r="I294" s="3" t="n"/>
       <c r="J294" s="3" t="n"/>
+      <c r="K294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="n"/>
@@ -9861,6 +10160,7 @@
       <c r="H295" s="3" t="n"/>
       <c r="I295" s="3" t="n"/>
       <c r="J295" s="3" t="n"/>
+      <c r="K295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="n"/>
@@ -9893,6 +10193,7 @@
       <c r="H296" s="3" t="n"/>
       <c r="I296" s="3" t="n"/>
       <c r="J296" s="3" t="n"/>
+      <c r="K296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="n"/>
@@ -9925,6 +10226,7 @@
       <c r="H297" s="3" t="n"/>
       <c r="I297" s="3" t="n"/>
       <c r="J297" s="3" t="n"/>
+      <c r="K297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="n"/>
@@ -9957,6 +10259,7 @@
       <c r="H298" s="3" t="n"/>
       <c r="I298" s="3" t="n"/>
       <c r="J298" s="3" t="n"/>
+      <c r="K298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="n"/>
@@ -9985,6 +10288,7 @@
       <c r="H299" s="3" t="n"/>
       <c r="I299" s="3" t="n"/>
       <c r="J299" s="3" t="n"/>
+      <c r="K299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="n"/>
@@ -10017,6 +10321,7 @@
       <c r="H300" s="3" t="n"/>
       <c r="I300" s="3" t="n"/>
       <c r="J300" s="3" t="n"/>
+      <c r="K300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="n"/>
@@ -10049,6 +10354,7 @@
       <c r="H301" s="3" t="n"/>
       <c r="I301" s="3" t="n"/>
       <c r="J301" s="3" t="n"/>
+      <c r="K301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="n"/>
@@ -10081,6 +10387,7 @@
       <c r="H302" s="3" t="n"/>
       <c r="I302" s="3" t="n"/>
       <c r="J302" s="3" t="n"/>
+      <c r="K302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="n"/>
@@ -10113,6 +10420,7 @@
       <c r="H303" s="3" t="n"/>
       <c r="I303" s="3" t="n"/>
       <c r="J303" s="3" t="n"/>
+      <c r="K303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="n"/>
@@ -10141,6 +10449,7 @@
       <c r="H304" s="3" t="n"/>
       <c r="I304" s="3" t="n"/>
       <c r="J304" s="3" t="n"/>
+      <c r="K304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="n"/>
@@ -10173,6 +10482,7 @@
       <c r="H305" s="3" t="n"/>
       <c r="I305" s="3" t="n"/>
       <c r="J305" s="3" t="n"/>
+      <c r="K305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="n"/>
@@ -10201,6 +10511,7 @@
       <c r="H306" s="3" t="n"/>
       <c r="I306" s="3" t="n"/>
       <c r="J306" s="3" t="n"/>
+      <c r="K306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="n"/>
@@ -10233,6 +10544,7 @@
       <c r="H307" s="3" t="n"/>
       <c r="I307" s="3" t="n"/>
       <c r="J307" s="3" t="n"/>
+      <c r="K307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="n"/>
@@ -10265,6 +10577,7 @@
       <c r="H308" s="3" t="n"/>
       <c r="I308" s="3" t="n"/>
       <c r="J308" s="3" t="n"/>
+      <c r="K308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="n"/>
@@ -10297,6 +10610,7 @@
       <c r="H309" s="3" t="n"/>
       <c r="I309" s="3" t="n"/>
       <c r="J309" s="3" t="n"/>
+      <c r="K309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="n"/>
@@ -10325,6 +10639,7 @@
       <c r="H310" s="3" t="n"/>
       <c r="I310" s="3" t="n"/>
       <c r="J310" s="3" t="n"/>
+      <c r="K310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="n"/>
@@ -10357,6 +10672,7 @@
       <c r="H311" s="3" t="n"/>
       <c r="I311" s="3" t="n"/>
       <c r="J311" s="3" t="n"/>
+      <c r="K311" s="3" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="n"/>
@@ -10389,6 +10705,7 @@
       <c r="H312" s="3" t="n"/>
       <c r="I312" s="3" t="n"/>
       <c r="J312" s="3" t="n"/>
+      <c r="K312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="n"/>
@@ -10421,6 +10738,7 @@
       <c r="H313" s="3" t="n"/>
       <c r="I313" s="3" t="n"/>
       <c r="J313" s="3" t="n"/>
+      <c r="K313" s="3" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="n"/>
@@ -10453,6 +10771,7 @@
       <c r="H314" s="3" t="n"/>
       <c r="I314" s="3" t="n"/>
       <c r="J314" s="3" t="n"/>
+      <c r="K314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="n"/>
@@ -10481,6 +10800,7 @@
       <c r="H315" s="3" t="n"/>
       <c r="I315" s="3" t="n"/>
       <c r="J315" s="3" t="n"/>
+      <c r="K315" s="3" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="n"/>
@@ -10513,6 +10833,7 @@
       <c r="H316" s="3" t="n"/>
       <c r="I316" s="3" t="n"/>
       <c r="J316" s="3" t="n"/>
+      <c r="K316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="n"/>
@@ -10545,6 +10866,7 @@
       <c r="H317" s="3" t="n"/>
       <c r="I317" s="3" t="n"/>
       <c r="J317" s="3" t="n"/>
+      <c r="K317" s="3" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="n"/>
@@ -10577,6 +10899,7 @@
       <c r="H318" s="3" t="n"/>
       <c r="I318" s="3" t="n"/>
       <c r="J318" s="3" t="n"/>
+      <c r="K318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="n"/>
@@ -10609,6 +10932,7 @@
       <c r="H319" s="3" t="n"/>
       <c r="I319" s="3" t="n"/>
       <c r="J319" s="3" t="n"/>
+      <c r="K319" s="3" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="n"/>
@@ -10641,6 +10965,7 @@
       <c r="H320" s="3" t="n"/>
       <c r="I320" s="3" t="n"/>
       <c r="J320" s="3" t="n"/>
+      <c r="K320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="n"/>
@@ -10673,6 +10998,7 @@
       <c r="H321" s="3" t="n"/>
       <c r="I321" s="3" t="n"/>
       <c r="J321" s="3" t="n"/>
+      <c r="K321" s="3" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="n"/>
@@ -10709,6 +11035,7 @@
           <t>#5</t>
         </is>
       </c>
+      <c r="K322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="n"/>
@@ -10741,6 +11068,7 @@
       <c r="H323" s="3" t="n"/>
       <c r="I323" s="3" t="n"/>
       <c r="J323" s="3" t="n"/>
+      <c r="K323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="n"/>
@@ -10773,6 +11101,7 @@
       <c r="H324" s="3" t="n"/>
       <c r="I324" s="3" t="n"/>
       <c r="J324" s="3" t="n"/>
+      <c r="K324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="n"/>
@@ -10805,6 +11134,7 @@
       <c r="H325" s="3" t="n"/>
       <c r="I325" s="3" t="n"/>
       <c r="J325" s="3" t="n"/>
+      <c r="K325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="n"/>
@@ -10837,6 +11167,7 @@
       <c r="H326" s="3" t="n"/>
       <c r="I326" s="3" t="n"/>
       <c r="J326" s="3" t="n"/>
+      <c r="K326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="n"/>
@@ -10869,6 +11200,7 @@
       <c r="H327" s="3" t="n"/>
       <c r="I327" s="3" t="n"/>
       <c r="J327" s="3" t="n"/>
+      <c r="K327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="n"/>
@@ -10901,6 +11233,7 @@
       <c r="H328" s="3" t="n"/>
       <c r="I328" s="3" t="n"/>
       <c r="J328" s="3" t="n"/>
+      <c r="K328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="n"/>
@@ -10929,6 +11262,7 @@
       <c r="H329" s="3" t="n"/>
       <c r="I329" s="3" t="n"/>
       <c r="J329" s="3" t="n"/>
+      <c r="K329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="n"/>
@@ -10961,6 +11295,7 @@
       <c r="H330" s="3" t="n"/>
       <c r="I330" s="3" t="n"/>
       <c r="J330" s="3" t="n"/>
+      <c r="K330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="n"/>
@@ -10993,6 +11328,7 @@
       <c r="H331" s="3" t="n"/>
       <c r="I331" s="3" t="n"/>
       <c r="J331" s="3" t="n"/>
+      <c r="K331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="n"/>
@@ -11025,6 +11361,7 @@
       <c r="H332" s="3" t="n"/>
       <c r="I332" s="3" t="n"/>
       <c r="J332" s="3" t="n"/>
+      <c r="K332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="n"/>
@@ -11057,6 +11394,7 @@
       <c r="H333" s="3" t="n"/>
       <c r="I333" s="3" t="n"/>
       <c r="J333" s="3" t="n"/>
+      <c r="K333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="n"/>
@@ -11101,6 +11439,7 @@
           <t>#22</t>
         </is>
       </c>
+      <c r="K334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="n"/>
@@ -11133,6 +11472,7 @@
       <c r="H335" s="3" t="n"/>
       <c r="I335" s="3" t="n"/>
       <c r="J335" s="3" t="n"/>
+      <c r="K335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="n"/>
@@ -11177,6 +11517,7 @@
           <t>#22</t>
         </is>
       </c>
+      <c r="K336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="n"/>
@@ -11209,6 +11550,7 @@
       <c r="H337" s="3" t="n"/>
       <c r="I337" s="3" t="n"/>
       <c r="J337" s="3" t="n"/>
+      <c r="K337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="n"/>
@@ -11241,6 +11583,7 @@
       <c r="H338" s="3" t="n"/>
       <c r="I338" s="3" t="n"/>
       <c r="J338" s="3" t="n"/>
+      <c r="K338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="n"/>
@@ -11273,6 +11616,7 @@
       <c r="H339" s="3" t="n"/>
       <c r="I339" s="3" t="n"/>
       <c r="J339" s="3" t="n"/>
+      <c r="K339" s="3" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="n"/>
@@ -11305,6 +11649,7 @@
       <c r="H340" s="3" t="n"/>
       <c r="I340" s="3" t="n"/>
       <c r="J340" s="3" t="n"/>
+      <c r="K340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="n"/>
@@ -11333,6 +11678,7 @@
       <c r="H341" s="3" t="n"/>
       <c r="I341" s="3" t="n"/>
       <c r="J341" s="3" t="n"/>
+      <c r="K341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="n"/>
@@ -11365,6 +11711,7 @@
       <c r="H342" s="3" t="n"/>
       <c r="I342" s="3" t="n"/>
       <c r="J342" s="3" t="n"/>
+      <c r="K342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="n"/>
@@ -11397,6 +11744,7 @@
       <c r="H343" s="3" t="n"/>
       <c r="I343" s="3" t="n"/>
       <c r="J343" s="3" t="n"/>
+      <c r="K343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="n"/>
@@ -11429,6 +11777,7 @@
       <c r="H344" s="3" t="n"/>
       <c r="I344" s="3" t="n"/>
       <c r="J344" s="3" t="n"/>
+      <c r="K344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="n"/>
@@ -11461,6 +11810,7 @@
       <c r="H345" s="3" t="n"/>
       <c r="I345" s="3" t="n"/>
       <c r="J345" s="3" t="n"/>
+      <c r="K345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="n"/>
@@ -11493,6 +11843,7 @@
       <c r="H346" s="3" t="n"/>
       <c r="I346" s="3" t="n"/>
       <c r="J346" s="3" t="n"/>
+      <c r="K346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="n"/>
@@ -11525,6 +11876,7 @@
       <c r="H347" s="3" t="n"/>
       <c r="I347" s="3" t="n"/>
       <c r="J347" s="3" t="n"/>
+      <c r="K347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="n"/>
@@ -11557,6 +11909,7 @@
       <c r="H348" s="3" t="n"/>
       <c r="I348" s="3" t="n"/>
       <c r="J348" s="3" t="n"/>
+      <c r="K348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="n"/>
@@ -11589,6 +11942,7 @@
       <c r="H349" s="3" t="n"/>
       <c r="I349" s="3" t="n"/>
       <c r="J349" s="3" t="n"/>
+      <c r="K349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="n"/>
@@ -11621,6 +11975,7 @@
       <c r="H350" s="3" t="n"/>
       <c r="I350" s="3" t="n"/>
       <c r="J350" s="3" t="n"/>
+      <c r="K350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="n"/>
@@ -11653,6 +12008,7 @@
       <c r="H351" s="3" t="n"/>
       <c r="I351" s="3" t="n"/>
       <c r="J351" s="3" t="n"/>
+      <c r="K351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="n"/>
@@ -11685,6 +12041,7 @@
       <c r="H352" s="3" t="n"/>
       <c r="I352" s="3" t="n"/>
       <c r="J352" s="3" t="n"/>
+      <c r="K352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="n"/>
@@ -11717,6 +12074,7 @@
       <c r="H353" s="3" t="n"/>
       <c r="I353" s="3" t="n"/>
       <c r="J353" s="3" t="n"/>
+      <c r="K353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="n"/>
@@ -11749,6 +12107,7 @@
       <c r="H354" s="3" t="n"/>
       <c r="I354" s="3" t="n"/>
       <c r="J354" s="3" t="n"/>
+      <c r="K354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="n"/>
@@ -11781,6 +12140,7 @@
       <c r="H355" s="3" t="n"/>
       <c r="I355" s="3" t="n"/>
       <c r="J355" s="3" t="n"/>
+      <c r="K355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="n"/>
@@ -11813,6 +12173,7 @@
       <c r="H356" s="3" t="n"/>
       <c r="I356" s="3" t="n"/>
       <c r="J356" s="3" t="n"/>
+      <c r="K356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="n"/>
@@ -11837,6 +12198,7 @@
       <c r="H357" s="3" t="n"/>
       <c r="I357" s="3" t="n"/>
       <c r="J357" s="3" t="n"/>
+      <c r="K357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="n"/>
@@ -11865,6 +12227,7 @@
       <c r="H358" s="3" t="n"/>
       <c r="I358" s="3" t="n"/>
       <c r="J358" s="3" t="n"/>
+      <c r="K358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="n"/>
@@ -11897,6 +12260,7 @@
       <c r="H359" s="3" t="n"/>
       <c r="I359" s="3" t="n"/>
       <c r="J359" s="3" t="n"/>
+      <c r="K359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="n"/>
@@ -11929,6 +12293,7 @@
       <c r="H360" s="3" t="n"/>
       <c r="I360" s="3" t="n"/>
       <c r="J360" s="3" t="n"/>
+      <c r="K360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="n"/>
@@ -11961,6 +12326,7 @@
       <c r="H361" s="3" t="n"/>
       <c r="I361" s="3" t="n"/>
       <c r="J361" s="3" t="n"/>
+      <c r="K361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="n"/>
@@ -11993,6 +12359,7 @@
       <c r="H362" s="3" t="n"/>
       <c r="I362" s="3" t="n"/>
       <c r="J362" s="3" t="n"/>
+      <c r="K362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="n"/>
@@ -12025,6 +12392,7 @@
       <c r="H363" s="3" t="n"/>
       <c r="I363" s="3" t="n"/>
       <c r="J363" s="3" t="n"/>
+      <c r="K363" s="3" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="n"/>
@@ -12057,6 +12425,7 @@
       <c r="H364" s="3" t="n"/>
       <c r="I364" s="3" t="n"/>
       <c r="J364" s="3" t="n"/>
+      <c r="K364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="n"/>
@@ -12089,6 +12458,7 @@
       <c r="H365" s="3" t="n"/>
       <c r="I365" s="3" t="n"/>
       <c r="J365" s="3" t="n"/>
+      <c r="K365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="n"/>
@@ -12121,6 +12491,7 @@
       <c r="H366" s="3" t="n"/>
       <c r="I366" s="3" t="n"/>
       <c r="J366" s="3" t="n"/>
+      <c r="K366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="n"/>
@@ -12153,6 +12524,7 @@
       <c r="H367" s="3" t="n"/>
       <c r="I367" s="3" t="n"/>
       <c r="J367" s="3" t="n"/>
+      <c r="K367" s="3" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="n"/>
@@ -12197,6 +12569,7 @@
           <t>#17</t>
         </is>
       </c>
+      <c r="K368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="n"/>
@@ -12229,6 +12602,7 @@
       <c r="H369" s="3" t="n"/>
       <c r="I369" s="3" t="n"/>
       <c r="J369" s="3" t="n"/>
+      <c r="K369" s="3" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="n"/>
@@ -12261,6 +12635,7 @@
       <c r="H370" s="3" t="n"/>
       <c r="I370" s="3" t="n"/>
       <c r="J370" s="3" t="n"/>
+      <c r="K370" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/terrestrial/Level3_20-Aug-26.xlsx
+++ b/terrestrial/Level3_20-Aug-26.xlsx
@@ -454,22 +454,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>L3 code</t>
+          <t>Local_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>L3 area</t>
+          <t>Full_name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>L2 code</t>
+          <t>Level_2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>L3 ISOcode</t>
+          <t>ISO_ter1</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">

--- a/terrestrial/Level3_20-Aug-26.xlsx
+++ b/terrestrial/Level3_20-Aug-26.xlsx
@@ -567,7 +567,11 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Alberta</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -611,7 +615,11 @@
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Afghanistan</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -655,7 +663,11 @@
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising AGE-BA, AGE-CH, AGE-CN, AGE-CO, AGE-DF, AGE-ER, AGE-FO, AGE-LP, AGE-MI, and AGE-SF.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -699,7 +711,11 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising AGS-CB, AGS-NE, AGS-RN, AGS-SC, and AGS-TF.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -743,7 +759,11 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising AGW-CA, AGW-JU, AGW-LR, AGW-ME, AGW-SA, AGW-SE, AGW-SJ, AGW-SL, and AGW-TU.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -787,7 +807,11 @@
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Alabama</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -831,7 +855,11 @@
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -875,7 +903,11 @@
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Aldabra Atoll, Seychelles</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -919,7 +951,11 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -963,7 +999,11 @@
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>Altai region of southern Siberia, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1007,7 +1047,11 @@
         </is>
       </c>
       <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Aleutian Islands, Alaska</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1051,7 +1095,11 @@
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Amur Oblast, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1091,7 +1139,11 @@
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising AND-AN and AND-CO.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1135,7 +1187,11 @@
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1179,7 +1235,11 @@
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Antarctica</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1223,7 +1283,11 @@
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Arizona</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1267,7 +1331,11 @@
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Arkansas</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1311,7 +1379,11 @@
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1355,7 +1427,11 @@
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Ascension Island</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1399,7 +1475,11 @@
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n"/>
       <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Alaska</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1443,7 +1523,11 @@
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam and Saint-Paul Islands, French Southern Territories</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1487,7 +1571,11 @@
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising ASS-AS, ASS-MA, ASS-ME, ASS-MI, ASS-NA, and ASS-TR.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1531,7 +1619,11 @@
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Antipodes Islands, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1571,7 +1663,11 @@
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n"/>
       <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising AUT-AU and AUT-LI.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1615,7 +1711,11 @@
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Azores, Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1659,7 +1759,11 @@
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>The Bahamas</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1703,7 +1807,11 @@
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Balearic Islands, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1747,7 +1855,11 @@
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
       <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1791,7 +1903,11 @@
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1835,7 +1951,11 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1875,7 +1995,11 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising BGM-BE and BGM-LU.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1919,7 +2043,11 @@
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n"/>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>Bismarck Archipelago, Papua New Guinea</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1963,7 +2091,11 @@
       <c r="K34" s="4" t="n"/>
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2007,7 +2139,11 @@
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2047,7 +2183,11 @@
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
       <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising BLT-ES, BLT-KA, BLT-LA, and BLT-LI.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2091,7 +2231,11 @@
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Belize</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2135,7 +2279,11 @@
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2175,7 +2323,11 @@
       <c r="K39" s="4" t="n"/>
       <c r="L39" s="4" t="n"/>
       <c r="M39" s="4" t="n"/>
-      <c r="N39" s="4" t="n"/>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising BOR-BR, BOR-KA, BOR-SB, and BOR-SR.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -2219,7 +2371,11 @@
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -2263,7 +2419,11 @@
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
       <c r="M41" s="4" t="n"/>
-      <c r="N41" s="4" t="n"/>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Bouvet Island, Norwegian sub-Antarctic territory</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2307,7 +2467,11 @@
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of British Columbia</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -2351,7 +2515,11 @@
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
       <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>Republic of Buryatia, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2395,7 +2563,11 @@
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2439,7 +2611,11 @@
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Burundi</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2483,7 +2659,11 @@
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
       <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising BZC-DF, BZC-GO, BZC-MS, and BZC-MT.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -2527,7 +2707,11 @@
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
       <c r="M47" s="4" t="n"/>
-      <c r="N47" s="4" t="n"/>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising BZE-AL, BZE-BA, BZE-CE, BZE-FN, BZE-MA, BZE-PB, BZE-PE, BZE-PI, BZE-RN, and BZE-SE.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -2571,7 +2755,11 @@
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising BZL-ES, BZL-MG, BZL-RJ, BZL-SP, and BZL-TR.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -2615,7 +2803,11 @@
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising BZN-AC, BZN-AM, BZN-AP, BZN-PA, BZN-RM, BZN-RO, and BZN-TO.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -2659,7 +2851,11 @@
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising BZS-PR, BZS-RS, and BZS-SC.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -2703,7 +2899,11 @@
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Cabinda, an Angolan exclave province</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -2747,7 +2947,11 @@
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>Central African Republic</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -2791,7 +2995,11 @@
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="4" t="n"/>
-      <c r="N53" s="4" t="n"/>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>California, USA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -2835,7 +3043,11 @@
       <c r="K54" s="4" t="n"/>
       <c r="L54" s="4" t="n"/>
       <c r="M54" s="4" t="n"/>
-      <c r="N54" s="4" t="n"/>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>The Cayman Islands</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -2879,7 +3091,11 @@
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -2923,7 +3139,11 @@
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
       <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="n"/>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>Chagos Archipelago, British Indian Ocean Territory</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -2967,7 +3187,11 @@
       <c r="K57" s="4" t="n"/>
       <c r="L57" s="4" t="n"/>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>Chad</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -3011,7 +3235,11 @@
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
       <c r="M58" s="4" t="n"/>
-      <c r="N58" s="4" t="n"/>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CHC-CQ, CHC-GZ, CHC-HU, CHC-SC, and CHC-YN.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -3055,7 +3283,11 @@
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n"/>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>Hainan province, China</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -3107,7 +3339,11 @@
           <t>#23</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n"/>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CHI-NM and CHI-NX.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -3159,7 +3395,11 @@
           <t>#23</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n"/>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CHM-HJ, CHM-JL, and CHM-LN.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -3211,7 +3451,11 @@
           <t>#23</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n"/>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CHN-BJ, CHN-GS, CHN-HB, CHN-SA, CHN-SD, CHN-SX, and CHN-TJ.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -3255,7 +3499,11 @@
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
       <c r="M63" s="4" t="n"/>
-      <c r="N63" s="4" t="n"/>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>Qinghai province, China</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -3307,7 +3555,11 @@
           <t>#23</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n"/>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CHS-AH, CHS-FJ, CHS-GD, CHS-GX, CHS-HE, CHS-HK, CHS-HN, CHS-JS, CHS-JX, CHS-KI, CHS-MA, CHS-MP, CHS-SH, and CHS-ZJ.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -3351,7 +3603,11 @@
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
       <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>Tibet Autonomous Region, China</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -3395,7 +3651,11 @@
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
       <c r="M66" s="4" t="n"/>
-      <c r="N66" s="4" t="n"/>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>Xinjiang Uyghur Autonomous Region, China</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -3439,7 +3699,11 @@
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
       <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="n"/>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>The Cocos (Keeling) Islands</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -3483,7 +3747,11 @@
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
-      <c r="N68" s="4" t="n"/>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CLC-BI, CLC-CO, CLC-LA, CLC-MA, CLC-NU, CLC-OH, CLC-SA, and CLC-VA.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -3527,7 +3795,11 @@
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
       <c r="M69" s="4" t="n"/>
-      <c r="N69" s="4" t="n"/>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -3571,7 +3843,11 @@
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
       <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="n"/>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CLN-AN, CLN-AT, CLN-TA, and CLN-AP.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -3615,7 +3891,11 @@
       <c r="K71" s="4" t="n"/>
       <c r="L71" s="4" t="n"/>
       <c r="M71" s="4" t="n"/>
-      <c r="N71" s="4" t="n"/>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CLS-AI, CLS-LL, and CLS-MG.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -3659,7 +3939,11 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -3703,7 +3987,11 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n"/>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Connecticut</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -3747,7 +4035,11 @@
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="n"/>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>Canary Islands, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -3791,7 +4083,11 @@
       <c r="K75" s="4" t="n"/>
       <c r="L75" s="4" t="n"/>
       <c r="M75" s="4" t="n"/>
-      <c r="N75" s="4" t="n"/>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -3831,7 +4127,11 @@
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="n"/>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising COM-CO and COM-MA.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -3875,7 +4175,11 @@
       <c r="K77" s="4" t="n"/>
       <c r="L77" s="4" t="n"/>
       <c r="M77" s="4" t="n"/>
-      <c r="N77" s="4" t="n"/>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>Republic of the Congo</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -3919,7 +4223,11 @@
       <c r="K78" s="4" t="n"/>
       <c r="L78" s="4" t="n"/>
       <c r="M78" s="4" t="n"/>
-      <c r="N78" s="4" t="n"/>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>Cook Islands</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -3963,7 +4271,11 @@
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
       <c r="M79" s="4" t="n"/>
-      <c r="N79" s="4" t="n"/>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>Corsica, France</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -4007,7 +4319,11 @@
       <c r="K80" s="4" t="n"/>
       <c r="L80" s="4" t="n"/>
       <c r="M80" s="4" t="n"/>
-      <c r="N80" s="4" t="n"/>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -4047,7 +4363,11 @@
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="n"/>
-      <c r="N81" s="4" t="n"/>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CPI-CL, CPI-CO, and CPI-MA.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -4091,7 +4411,11 @@
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
       <c r="M82" s="4" t="n"/>
-      <c r="N82" s="4" t="n"/>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CPP-EC, CPP-NC, and CPP-WC.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -4135,7 +4459,11 @@
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
-      <c r="N83" s="4" t="n"/>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>Caprivi Strip, Namibia</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -4175,7 +4503,11 @@
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
       <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="n"/>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CRL-MF and CRL-PA.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -4219,7 +4551,11 @@
       <c r="K85" s="4" t="n"/>
       <c r="L85" s="4" t="n"/>
       <c r="M85" s="4" t="n"/>
-      <c r="N85" s="4" t="n"/>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>Crozet Islands, French Southern Territories</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -4271,7 +4607,11 @@
           <t>#30</t>
         </is>
       </c>
-      <c r="N86" s="4" t="n"/>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>Zabaykalsky Krai, Russia (Transbaikal region)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -4315,7 +4655,11 @@
       <c r="K87" s="4" t="n"/>
       <c r="L87" s="4" t="n"/>
       <c r="M87" s="4" t="n"/>
-      <c r="N87" s="4" t="n"/>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>Chatham Islands, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -4359,7 +4703,11 @@
       <c r="K88" s="4" t="n"/>
       <c r="L88" s="4" t="n"/>
       <c r="M88" s="4" t="n"/>
-      <c r="N88" s="4" t="n"/>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -4403,7 +4751,11 @@
       <c r="K89" s="4" t="n"/>
       <c r="L89" s="4" t="n"/>
       <c r="M89" s="4" t="n"/>
-      <c r="N89" s="4" t="n"/>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>Cabo Verde (Cape Verde)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -4447,7 +4799,11 @@
       <c r="K90" s="4" t="n"/>
       <c r="L90" s="4" t="n"/>
       <c r="M90" s="4" t="n"/>
-      <c r="N90" s="4" t="n"/>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -4495,7 +4851,11 @@
           <t>#20</t>
         </is>
       </c>
-      <c r="N91" s="4" t="n"/>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising CZE-CZ and CZE-SK.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -4539,7 +4899,11 @@
       <c r="K92" s="4" t="n"/>
       <c r="L92" s="4" t="n"/>
       <c r="M92" s="4" t="n"/>
-      <c r="N92" s="4" t="n"/>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Delaware</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -4583,7 +4947,11 @@
       <c r="K93" s="4" t="n"/>
       <c r="L93" s="4" t="n"/>
       <c r="M93" s="4" t="n"/>
-      <c r="N93" s="4" t="n"/>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -4627,7 +4995,11 @@
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="4" t="n"/>
       <c r="M94" s="4" t="n"/>
-      <c r="N94" s="4" t="n"/>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>Djibouti</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -4671,7 +5043,11 @@
       <c r="K95" s="4" t="n"/>
       <c r="L95" s="4" t="n"/>
       <c r="M95" s="4" t="n"/>
-      <c r="N95" s="4" t="n"/>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -4715,7 +5091,11 @@
       <c r="K96" s="4" t="n"/>
       <c r="L96" s="4" t="n"/>
       <c r="M96" s="4" t="n"/>
-      <c r="N96" s="4" t="n"/>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>Desventuradas Islands, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -4759,7 +5139,11 @@
       <c r="K97" s="4" t="n"/>
       <c r="L97" s="4" t="n"/>
       <c r="M97" s="4" t="n"/>
-      <c r="N97" s="4" t="n"/>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>East Aegean Islands, Greece</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -4803,7 +5187,11 @@
       <c r="K98" s="4" t="n"/>
       <c r="L98" s="4" t="n"/>
       <c r="M98" s="4" t="n"/>
-      <c r="N98" s="4" t="n"/>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>Easter Island, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -4847,7 +5235,11 @@
       <c r="K99" s="4" t="n"/>
       <c r="L99" s="4" t="n"/>
       <c r="M99" s="4" t="n"/>
-      <c r="N99" s="4" t="n"/>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>Ecuador (mainland)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -4891,7 +5283,11 @@
       <c r="K100" s="4" t="n"/>
       <c r="L100" s="4" t="n"/>
       <c r="M100" s="4" t="n"/>
-      <c r="N100" s="4" t="n"/>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -4931,7 +5327,11 @@
       <c r="K101" s="4" t="n"/>
       <c r="L101" s="4" t="n"/>
       <c r="M101" s="4" t="n"/>
-      <c r="N101" s="4" t="n"/>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising EHM-AP, EHM-BH, EHM-DJ, and EHM-SI.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -4975,7 +5375,11 @@
       <c r="K102" s="4" t="n"/>
       <c r="L102" s="4" t="n"/>
       <c r="M102" s="4" t="n"/>
-      <c r="N102" s="4" t="n"/>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -5019,7 +5423,11 @@
       <c r="K103" s="4" t="n"/>
       <c r="L103" s="4" t="n"/>
       <c r="M103" s="4" t="n"/>
-      <c r="N103" s="4" t="n"/>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>Equatorial Guinea (mainland Río Muni)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -5063,7 +5471,11 @@
       <c r="K104" s="4" t="n"/>
       <c r="L104" s="4" t="n"/>
       <c r="M104" s="4" t="n"/>
-      <c r="N104" s="4" t="n"/>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>Eritrea</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -5119,7 +5531,11 @@
           <t>#12</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n"/>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>Eswatini (Swaziland)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -5163,7 +5579,11 @@
       <c r="K106" s="4" t="n"/>
       <c r="L106" s="4" t="n"/>
       <c r="M106" s="4" t="n"/>
-      <c r="N106" s="4" t="n"/>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -5207,7 +5627,11 @@
       <c r="K107" s="4" t="n"/>
       <c r="L107" s="4" t="n"/>
       <c r="M107" s="4" t="n"/>
-      <c r="N107" s="4" t="n"/>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>Falkland Islands (Malvinas)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -5251,7 +5675,11 @@
       <c r="K108" s="4" t="n"/>
       <c r="L108" s="4" t="n"/>
       <c r="M108" s="4" t="n"/>
-      <c r="N108" s="4" t="n"/>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -5295,7 +5723,11 @@
       <c r="K109" s="4" t="n"/>
       <c r="L109" s="4" t="n"/>
       <c r="M109" s="4" t="n"/>
-      <c r="N109" s="4" t="n"/>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -5339,7 +5771,11 @@
       <c r="K110" s="4" t="n"/>
       <c r="L110" s="4" t="n"/>
       <c r="M110" s="4" t="n"/>
-      <c r="N110" s="4" t="n"/>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Florida</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -5383,7 +5819,11 @@
       <c r="K111" s="4" t="n"/>
       <c r="L111" s="4" t="n"/>
       <c r="M111" s="4" t="n"/>
-      <c r="N111" s="4" t="n"/>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>Faroe Islands</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -5423,7 +5863,11 @@
       <c r="K112" s="4" t="n"/>
       <c r="L112" s="4" t="n"/>
       <c r="M112" s="4" t="n"/>
-      <c r="N112" s="4" t="n"/>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising FRA-CI, FRA-FR, and FRA-MO.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -5467,7 +5911,11 @@
       <c r="K113" s="4" t="n"/>
       <c r="L113" s="4" t="n"/>
       <c r="M113" s="4" t="n"/>
-      <c r="N113" s="4" t="n"/>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>French Guiana</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -5511,7 +5959,11 @@
       <c r="K114" s="4" t="n"/>
       <c r="L114" s="4" t="n"/>
       <c r="M114" s="4" t="n"/>
-      <c r="N114" s="4" t="n"/>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -5555,7 +6007,11 @@
       <c r="K115" s="4" t="n"/>
       <c r="L115" s="4" t="n"/>
       <c r="M115" s="4" t="n"/>
-      <c r="N115" s="4" t="n"/>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>Galápagos Islands, Ecuador</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -5599,7 +6055,11 @@
       <c r="K116" s="4" t="n"/>
       <c r="L116" s="4" t="n"/>
       <c r="M116" s="4" t="n"/>
-      <c r="N116" s="4" t="n"/>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>The Gambia</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -5643,7 +6103,11 @@
       <c r="K117" s="4" t="n"/>
       <c r="L117" s="4" t="n"/>
       <c r="M117" s="4" t="n"/>
-      <c r="N117" s="4" t="n"/>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Georgia</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -5687,7 +6151,11 @@
       <c r="K118" s="4" t="n"/>
       <c r="L118" s="4" t="n"/>
       <c r="M118" s="4" t="n"/>
-      <c r="N118" s="4" t="n"/>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -5727,7 +6195,11 @@
       <c r="K119" s="4" t="n"/>
       <c r="L119" s="4" t="n"/>
       <c r="M119" s="4" t="n"/>
-      <c r="N119" s="4" t="n"/>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising GGI-AN, GGI-BI, GGI-PR, and GGI-ST.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -5771,7 +6243,11 @@
       <c r="K120" s="4" t="n"/>
       <c r="L120" s="4" t="n"/>
       <c r="M120" s="4" t="n"/>
-      <c r="N120" s="4" t="n"/>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -5815,7 +6291,11 @@
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="n"/>
       <c r="M121" s="4" t="n"/>
-      <c r="N121" s="4" t="n"/>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>Gilbert Islands, Kiribati</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -5859,7 +6339,11 @@
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="n"/>
       <c r="M122" s="4" t="n"/>
-      <c r="N122" s="4" t="n"/>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>Guinea-Bissau</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -5903,7 +6387,11 @@
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="4" t="n"/>
       <c r="M123" s="4" t="n"/>
-      <c r="N123" s="4" t="n"/>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>Greenland</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -5947,7 +6435,11 @@
       <c r="K124" s="4" t="n"/>
       <c r="L124" s="4" t="n"/>
       <c r="M124" s="4" t="n"/>
-      <c r="N124" s="4" t="n"/>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>Great Britain (England, Scotland, Wales)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -5991,7 +6483,11 @@
       <c r="K125" s="4" t="n"/>
       <c r="L125" s="4" t="n"/>
       <c r="M125" s="4" t="n"/>
-      <c r="N125" s="4" t="n"/>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>Greece, excluding Crete</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -6031,7 +6527,11 @@
       <c r="K126" s="4" t="n"/>
       <c r="L126" s="4" t="n"/>
       <c r="M126" s="4" t="n"/>
-      <c r="N126" s="4" t="n"/>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising GST-BA, GST-QA, and GST-UA.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -6075,7 +6575,11 @@
       <c r="K127" s="4" t="n"/>
       <c r="L127" s="4" t="n"/>
       <c r="M127" s="4" t="n"/>
-      <c r="N127" s="4" t="n"/>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -6119,7 +6623,11 @@
       <c r="K128" s="4" t="n"/>
       <c r="L128" s="4" t="n"/>
       <c r="M128" s="4" t="n"/>
-      <c r="N128" s="4" t="n"/>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>Guinea, West Africa</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -6163,7 +6671,11 @@
       <c r="K129" s="4" t="n"/>
       <c r="L129" s="4" t="n"/>
       <c r="M129" s="4" t="n"/>
-      <c r="N129" s="4" t="n"/>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -6203,7 +6715,11 @@
       <c r="K130" s="4" t="n"/>
       <c r="L130" s="4" t="n"/>
       <c r="M130" s="4" t="n"/>
-      <c r="N130" s="4" t="n"/>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising HAI-HA and HAI-NI.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -6243,7 +6759,11 @@
       <c r="K131" s="4" t="n"/>
       <c r="L131" s="4" t="n"/>
       <c r="M131" s="4" t="n"/>
-      <c r="N131" s="4" t="n"/>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising HAW-HI, HAW-JI, and HAW-MI.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -6287,7 +6807,11 @@
       <c r="K132" s="4" t="n"/>
       <c r="L132" s="4" t="n"/>
       <c r="M132" s="4" t="n"/>
-      <c r="N132" s="4" t="n"/>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>Howland and Baker Islands, US Pacific territories</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -6331,7 +6855,11 @@
       <c r="K133" s="4" t="n"/>
       <c r="L133" s="4" t="n"/>
       <c r="M133" s="4" t="n"/>
-      <c r="N133" s="4" t="n"/>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>Heard Island and McDonald Islands, Australian external territory</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -6375,7 +6903,11 @@
       <c r="K134" s="4" t="n"/>
       <c r="L134" s="4" t="n"/>
       <c r="M134" s="4" t="n"/>
-      <c r="N134" s="4" t="n"/>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -6419,7 +6951,11 @@
       <c r="K135" s="4" t="n"/>
       <c r="L135" s="4" t="n"/>
       <c r="M135" s="4" t="n"/>
-      <c r="N135" s="4" t="n"/>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -6463,7 +6999,11 @@
       <c r="K136" s="4" t="n"/>
       <c r="L136" s="4" t="n"/>
       <c r="M136" s="4" t="n"/>
-      <c r="N136" s="4" t="n"/>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -6507,7 +7047,11 @@
       <c r="K137" s="4" t="n"/>
       <c r="L137" s="4" t="n"/>
       <c r="M137" s="4" t="n"/>
-      <c r="N137" s="4" t="n"/>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>Idaho, USA</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -6551,7 +7095,11 @@
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="4" t="n"/>
       <c r="M138" s="4" t="n"/>
-      <c r="N138" s="4" t="n"/>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>Illinois, USA</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -6595,7 +7143,11 @@
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="4" t="n"/>
       <c r="M139" s="4" t="n"/>
-      <c r="N139" s="4" t="n"/>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising IND-AP, IND-BI, IND-CH, IND-CT, IND-DD, IND-DE, IND-DI, IND-DM, IND-GO, IND-GU, IND-HA, IND-JK, IND-KE, IND-KL, IND-KT, IND-MH, IND-MP, IND-MR, IND-OR, IND-PO, IND-PU, IND-RA, IND-TN, IND-UP, IND-WB, IND-YA, and IND-TS.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -6639,7 +7191,11 @@
       <c r="K140" s="4" t="n"/>
       <c r="L140" s="4" t="n"/>
       <c r="M140" s="4" t="n"/>
-      <c r="N140" s="4" t="n"/>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>Indiana, USA</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -6683,7 +7239,11 @@
       <c r="K141" s="4" t="n"/>
       <c r="L141" s="4" t="n"/>
       <c r="M141" s="4" t="n"/>
-      <c r="N141" s="4" t="n"/>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>Iowa, USA</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -6723,7 +7283,11 @@
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="4" t="n"/>
       <c r="M142" s="4" t="n"/>
-      <c r="N142" s="4" t="n"/>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising IRE-IR and IRE-NI.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -6767,7 +7331,11 @@
       <c r="K143" s="4" t="n"/>
       <c r="L143" s="4" t="n"/>
       <c r="M143" s="4" t="n"/>
-      <c r="N143" s="4" t="n"/>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>Irkutsk Oblast, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -6811,7 +7379,11 @@
       <c r="K144" s="4" t="n"/>
       <c r="L144" s="4" t="n"/>
       <c r="M144" s="4" t="n"/>
-      <c r="N144" s="4" t="n"/>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -6855,7 +7427,11 @@
       <c r="K145" s="4" t="n"/>
       <c r="L145" s="4" t="n"/>
       <c r="M145" s="4" t="n"/>
-      <c r="N145" s="4" t="n"/>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>Iraq</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -6895,7 +7471,11 @@
       <c r="K146" s="4" t="n"/>
       <c r="L146" s="4" t="n"/>
       <c r="M146" s="4" t="n"/>
-      <c r="N146" s="4" t="n"/>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising ITA-IT, ITA-SM, and ITA-VC.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -6939,7 +7519,11 @@
       <c r="K147" s="4" t="n"/>
       <c r="L147" s="4" t="n"/>
       <c r="M147" s="4" t="n"/>
-      <c r="N147" s="4" t="n"/>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire (Ivory Coast)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -6983,7 +7567,11 @@
       <c r="K148" s="4" t="n"/>
       <c r="L148" s="4" t="n"/>
       <c r="M148" s="4" t="n"/>
-      <c r="N148" s="4" t="n"/>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -7027,7 +7615,11 @@
       <c r="K149" s="4" t="n"/>
       <c r="L149" s="4" t="n"/>
       <c r="M149" s="4" t="n"/>
-      <c r="N149" s="4" t="n"/>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising JAP-HK, JAP-HN, JAP-KY, and JAP-SH.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -7071,7 +7663,11 @@
       <c r="K150" s="4" t="n"/>
       <c r="L150" s="4" t="n"/>
       <c r="M150" s="4" t="n"/>
-      <c r="N150" s="4" t="n"/>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>Java, Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -7115,7 +7711,11 @@
       <c r="K151" s="4" t="n"/>
       <c r="L151" s="4" t="n"/>
       <c r="M151" s="4" t="n"/>
-      <c r="N151" s="4" t="n"/>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>Juan Fernández Islands, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -7159,7 +7759,11 @@
       <c r="K152" s="4" t="n"/>
       <c r="L152" s="4" t="n"/>
       <c r="M152" s="4" t="n"/>
-      <c r="N152" s="4" t="n"/>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>Kamchatka Krai, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -7203,7 +7807,11 @@
       <c r="K153" s="4" t="n"/>
       <c r="L153" s="4" t="n"/>
       <c r="M153" s="4" t="n"/>
-      <c r="N153" s="4" t="n"/>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>Kansas, USA</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -7247,7 +7855,11 @@
       <c r="K154" s="4" t="n"/>
       <c r="L154" s="4" t="n"/>
       <c r="M154" s="4" t="n"/>
-      <c r="N154" s="4" t="n"/>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -7291,7 +7903,11 @@
       <c r="K155" s="4" t="n"/>
       <c r="L155" s="4" t="n"/>
       <c r="M155" s="4" t="n"/>
-      <c r="N155" s="4" t="n"/>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>Kerguelen Islands, French Southern Territories</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -7335,7 +7951,11 @@
       <c r="K156" s="4" t="n"/>
       <c r="L156" s="4" t="n"/>
       <c r="M156" s="4" t="n"/>
-      <c r="N156" s="4" t="n"/>
+      <c r="N156" s="4" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -7379,7 +7999,11 @@
       <c r="K157" s="4" t="n"/>
       <c r="L157" s="4" t="n"/>
       <c r="M157" s="4" t="n"/>
-      <c r="N157" s="4" t="n"/>
+      <c r="N157" s="4" t="inlineStr">
+        <is>
+          <t>Kermadec Islands, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -7423,7 +8047,11 @@
       <c r="K158" s="4" t="n"/>
       <c r="L158" s="4" t="n"/>
       <c r="M158" s="4" t="n"/>
-      <c r="N158" s="4" t="n"/>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>Kyrgyzstan</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -7467,7 +8095,11 @@
       <c r="K159" s="4" t="n"/>
       <c r="L159" s="4" t="n"/>
       <c r="M159" s="4" t="n"/>
-      <c r="N159" s="4" t="n"/>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>Khabarovsk Krai, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -7507,7 +8139,11 @@
       <c r="K160" s="4" t="n"/>
       <c r="L160" s="4" t="n"/>
       <c r="M160" s="4" t="n"/>
-      <c r="N160" s="4" t="n"/>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising KOR-NK and KOR-SK.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -7551,7 +8187,11 @@
       <c r="K161" s="4" t="n"/>
       <c r="L161" s="4" t="n"/>
       <c r="M161" s="4" t="n"/>
-      <c r="N161" s="4" t="n"/>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>Krasnoyarsk Krai, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -7595,7 +8235,11 @@
       <c r="K162" s="4" t="n"/>
       <c r="L162" s="4" t="n"/>
       <c r="M162" s="4" t="n"/>
-      <c r="N162" s="4" t="n"/>
+      <c r="N162" s="4" t="inlineStr">
+        <is>
+          <t>Crete, Greece</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -7647,7 +8291,11 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="N163" s="4" t="n"/>
+      <c r="N163" s="4" t="inlineStr">
+        <is>
+          <t>Crimea</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -7691,7 +8339,11 @@
       <c r="K164" s="4" t="n"/>
       <c r="L164" s="4" t="n"/>
       <c r="M164" s="4" t="n"/>
-      <c r="N164" s="4" t="n"/>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>Kentucky, USA</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -7735,7 +8387,11 @@
       <c r="K165" s="4" t="n"/>
       <c r="L165" s="4" t="n"/>
       <c r="M165" s="4" t="n"/>
-      <c r="N165" s="4" t="n"/>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>Kuril Islands, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -7779,7 +8435,11 @@
       <c r="K166" s="4" t="n"/>
       <c r="L166" s="4" t="n"/>
       <c r="M166" s="4" t="n"/>
-      <c r="N166" s="4" t="n"/>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -7823,7 +8483,11 @@
       <c r="K167" s="4" t="n"/>
       <c r="L167" s="4" t="n"/>
       <c r="M167" s="4" t="n"/>
-      <c r="N167" s="4" t="n"/>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>Kazan Islands (Volcano Islands), Japan</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -7867,7 +8531,11 @@
       <c r="K168" s="4" t="n"/>
       <c r="L168" s="4" t="n"/>
       <c r="M168" s="4" t="n"/>
-      <c r="N168" s="4" t="n"/>
+      <c r="N168" s="4" t="inlineStr">
+        <is>
+          <t>Labrador, Canada</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -7911,7 +8579,11 @@
       <c r="K169" s="4" t="n"/>
       <c r="L169" s="4" t="n"/>
       <c r="M169" s="4" t="n"/>
-      <c r="N169" s="4" t="n"/>
+      <c r="N169" s="4" t="inlineStr">
+        <is>
+          <t>Laos</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -7955,7 +8627,11 @@
       <c r="K170" s="4" t="n"/>
       <c r="L170" s="4" t="n"/>
       <c r="M170" s="4" t="n"/>
-      <c r="N170" s="4" t="n"/>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -7995,7 +8671,11 @@
       <c r="K171" s="4" t="n"/>
       <c r="L171" s="4" t="n"/>
       <c r="M171" s="4" t="n"/>
-      <c r="N171" s="4" t="n"/>
+      <c r="N171" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising LBS-LB and LBS-SY.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -8039,7 +8719,11 @@
       <c r="K172" s="4" t="n"/>
       <c r="L172" s="4" t="n"/>
       <c r="M172" s="4" t="n"/>
-      <c r="N172" s="4" t="n"/>
+      <c r="N172" s="4" t="inlineStr">
+        <is>
+          <t>Libya</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -8083,7 +8767,11 @@
       <c r="K173" s="4" t="n"/>
       <c r="L173" s="4" t="n"/>
       <c r="M173" s="4" t="n"/>
-      <c r="N173" s="4" t="n"/>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>Laccadive Islands (Lakshadweep), India</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -8123,7 +8811,11 @@
       <c r="K174" s="4" t="n"/>
       <c r="L174" s="4" t="n"/>
       <c r="M174" s="4" t="n"/>
-      <c r="N174" s="4" t="n"/>
+      <c r="N174" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising LEE-AB, LEE-AG, LEE-AV, LEE-BV, LEE-GU, LEE-MO, LEE-NL, LEE-SK, LEE-SM, and LEE-VI.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -8167,7 +8859,11 @@
       <c r="K175" s="4" t="n"/>
       <c r="L175" s="4" t="n"/>
       <c r="M175" s="4" t="n"/>
-      <c r="N175" s="4" t="n"/>
+      <c r="N175" s="4" t="inlineStr">
+        <is>
+          <t>Lesotho</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -8207,7 +8903,11 @@
       <c r="K176" s="4" t="n"/>
       <c r="L176" s="4" t="n"/>
       <c r="M176" s="4" t="n"/>
-      <c r="N176" s="4" t="n"/>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising LIN-KI and LIN-US.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -8251,7 +8951,11 @@
       <c r="K177" s="4" t="n"/>
       <c r="L177" s="4" t="n"/>
       <c r="M177" s="4" t="n"/>
-      <c r="N177" s="4" t="n"/>
+      <c r="N177" s="4" t="inlineStr">
+        <is>
+          <t>Louisiana, USA</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -8291,7 +8995,11 @@
       <c r="K178" s="4" t="n"/>
       <c r="L178" s="4" t="n"/>
       <c r="M178" s="4" t="n"/>
-      <c r="N178" s="4" t="n"/>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising LSI-BA, LSI-ET, LSI-LS, and LSI-WT.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -8335,7 +9043,11 @@
       <c r="K179" s="4" t="n"/>
       <c r="L179" s="4" t="n"/>
       <c r="M179" s="4" t="n"/>
-      <c r="N179" s="4" t="n"/>
+      <c r="N179" s="4" t="inlineStr">
+        <is>
+          <t>Magadan Oblast, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -8379,7 +9091,11 @@
       <c r="K180" s="4" t="n"/>
       <c r="L180" s="4" t="n"/>
       <c r="M180" s="4" t="n"/>
-      <c r="N180" s="4" t="n"/>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>Maine, USA</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -8423,7 +9139,11 @@
       <c r="K181" s="4" t="n"/>
       <c r="L181" s="4" t="n"/>
       <c r="M181" s="4" t="n"/>
-      <c r="N181" s="4" t="n"/>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>Manitoba, Canada</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -8467,7 +9187,11 @@
       <c r="K182" s="4" t="n"/>
       <c r="L182" s="4" t="n"/>
       <c r="M182" s="4" t="n"/>
-      <c r="N182" s="4" t="n"/>
+      <c r="N182" s="4" t="inlineStr">
+        <is>
+          <t>Macquarie Island, Australia</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -8511,7 +9235,11 @@
       <c r="K183" s="4" t="n"/>
       <c r="L183" s="4" t="n"/>
       <c r="M183" s="4" t="n"/>
-      <c r="N183" s="4" t="n"/>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>Massachusetts, USA</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -8555,7 +9283,11 @@
       <c r="K184" s="4" t="n"/>
       <c r="L184" s="4" t="n"/>
       <c r="M184" s="4" t="n"/>
-      <c r="N184" s="4" t="n"/>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -8600,7 +9332,11 @@
         </is>
       </c>
       <c r="M185" s="4" t="n"/>
-      <c r="N185" s="4" t="n"/>
+      <c r="N185" s="4" t="inlineStr">
+        <is>
+          <t>Scattered Islands in the Mozambique Channel</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -8644,7 +9380,11 @@
       <c r="K186" s="4" t="n"/>
       <c r="L186" s="4" t="n"/>
       <c r="M186" s="4" t="n"/>
-      <c r="N186" s="4" t="n"/>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>Marcus Island (Minami-Tori-shima), Japan</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -8688,7 +9428,11 @@
       <c r="K187" s="4" t="n"/>
       <c r="L187" s="4" t="n"/>
       <c r="M187" s="4" t="n"/>
-      <c r="N187" s="4" t="n"/>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>Madagascar</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -8732,7 +9476,11 @@
       <c r="K188" s="4" t="n"/>
       <c r="L188" s="4" t="n"/>
       <c r="M188" s="4" t="n"/>
-      <c r="N188" s="4" t="n"/>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>Madeira, Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -8776,7 +9524,11 @@
       <c r="K189" s="4" t="n"/>
       <c r="L189" s="4" t="n"/>
       <c r="M189" s="4" t="n"/>
-      <c r="N189" s="4" t="n"/>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -8820,7 +9572,11 @@
       <c r="K190" s="4" t="n"/>
       <c r="L190" s="4" t="n"/>
       <c r="M190" s="4" t="n"/>
-      <c r="N190" s="4" t="n"/>
+      <c r="N190" s="4" t="inlineStr">
+        <is>
+          <t>Michigan, USA</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -8864,7 +9620,11 @@
       <c r="K191" s="4" t="n"/>
       <c r="L191" s="4" t="n"/>
       <c r="M191" s="4" t="n"/>
-      <c r="N191" s="4" t="n"/>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>Minnesota, USA</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -8908,7 +9668,11 @@
       <c r="K192" s="4" t="n"/>
       <c r="L192" s="4" t="n"/>
       <c r="M192" s="4" t="n"/>
-      <c r="N192" s="4" t="n"/>
+      <c r="N192" s="4" t="inlineStr">
+        <is>
+          <t>Mali</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -8952,7 +9716,11 @@
       <c r="K193" s="4" t="n"/>
       <c r="L193" s="4" t="n"/>
       <c r="M193" s="4" t="n"/>
-      <c r="N193" s="4" t="n"/>
+      <c r="N193" s="4" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -8992,7 +9760,11 @@
       <c r="K194" s="4" t="n"/>
       <c r="L194" s="4" t="n"/>
       <c r="M194" s="4" t="n"/>
-      <c r="N194" s="4" t="n"/>
+      <c r="N194" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising MLY-PM and MLY-SI.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -9036,7 +9808,11 @@
       <c r="K195" s="4" t="n"/>
       <c r="L195" s="4" t="n"/>
       <c r="M195" s="4" t="n"/>
-      <c r="N195" s="4" t="n"/>
+      <c r="N195" s="4" t="inlineStr">
+        <is>
+          <t>Montana, USA</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -9080,7 +9856,11 @@
       <c r="K196" s="4" t="n"/>
       <c r="L196" s="4" t="n"/>
       <c r="M196" s="4" t="n"/>
-      <c r="N196" s="4" t="n"/>
+      <c r="N196" s="4" t="inlineStr">
+        <is>
+          <t>Maluku Islands (Moluccas), Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -9124,7 +9904,11 @@
       <c r="K197" s="4" t="n"/>
       <c r="L197" s="4" t="n"/>
       <c r="M197" s="4" t="n"/>
-      <c r="N197" s="4" t="n"/>
+      <c r="N197" s="4" t="inlineStr">
+        <is>
+          <t>Mongolia</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -9164,7 +9948,11 @@
       <c r="K198" s="4" t="n"/>
       <c r="L198" s="4" t="n"/>
       <c r="M198" s="4" t="n"/>
-      <c r="N198" s="4" t="n"/>
+      <c r="N198" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising MOR-MO and MOR-SP.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -9208,7 +9996,11 @@
       <c r="K199" s="4" t="n"/>
       <c r="L199" s="4" t="n"/>
       <c r="M199" s="4" t="n"/>
-      <c r="N199" s="4" t="n"/>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -9252,7 +10044,11 @@
       <c r="K200" s="4" t="n"/>
       <c r="L200" s="4" t="n"/>
       <c r="M200" s="4" t="n"/>
-      <c r="N200" s="4" t="n"/>
+      <c r="N200" s="4" t="inlineStr">
+        <is>
+          <t>Marion and Prince Edward Islands, South Africa</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -9292,7 +10088,11 @@
       <c r="K201" s="4" t="n"/>
       <c r="L201" s="4" t="n"/>
       <c r="M201" s="4" t="n"/>
-      <c r="N201" s="4" t="n"/>
+      <c r="N201" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising MRN-GU and MRN-NM.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -9336,7 +10136,11 @@
       <c r="K202" s="4" t="n"/>
       <c r="L202" s="4" t="n"/>
       <c r="M202" s="4" t="n"/>
-      <c r="N202" s="4" t="n"/>
+      <c r="N202" s="4" t="inlineStr">
+        <is>
+          <t>Marquesas Islands, French Polynesia</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -9380,7 +10184,11 @@
       <c r="K203" s="4" t="n"/>
       <c r="L203" s="4" t="n"/>
       <c r="M203" s="4" t="n"/>
-      <c r="N203" s="4" t="n"/>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>Marshall Islands</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -9424,7 +10232,11 @@
       <c r="K204" s="4" t="n"/>
       <c r="L204" s="4" t="n"/>
       <c r="M204" s="4" t="n"/>
-      <c r="N204" s="4" t="n"/>
+      <c r="N204" s="4" t="inlineStr">
+        <is>
+          <t>Maryland, USA</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -9468,7 +10280,11 @@
       <c r="K205" s="4" t="n"/>
       <c r="L205" s="4" t="n"/>
       <c r="M205" s="4" t="n"/>
-      <c r="N205" s="4" t="n"/>
+      <c r="N205" s="4" t="inlineStr">
+        <is>
+          <t>Mississippi, USA</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -9512,7 +10328,11 @@
       <c r="K206" s="4" t="n"/>
       <c r="L206" s="4" t="n"/>
       <c r="M206" s="4" t="n"/>
-      <c r="N206" s="4" t="n"/>
+      <c r="N206" s="4" t="inlineStr">
+        <is>
+          <t>Missouri, USA</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -9556,7 +10376,11 @@
       <c r="K207" s="4" t="n"/>
       <c r="L207" s="4" t="n"/>
       <c r="M207" s="4" t="n"/>
-      <c r="N207" s="4" t="n"/>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -9600,7 +10424,11 @@
       <c r="K208" s="4" t="n"/>
       <c r="L208" s="4" t="n"/>
       <c r="M208" s="4" t="n"/>
-      <c r="N208" s="4" t="n"/>
+      <c r="N208" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising MXC-DF, MXC-ME, MXC-MO, MXC-PU, and MXC-TL.</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -9644,7 +10472,11 @@
       <c r="K209" s="4" t="n"/>
       <c r="L209" s="4" t="n"/>
       <c r="M209" s="4" t="n"/>
-      <c r="N209" s="4" t="n"/>
+      <c r="N209" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising MXE-AG, MXE-CO, MXE-CU, MXE-DU, MXE-GU, MXE-HI, MXE-NL, MXE-QU, MXE-SL, MXE-TA, and MXE-ZA.</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -9688,7 +10520,11 @@
       <c r="K210" s="4" t="n"/>
       <c r="L210" s="4" t="n"/>
       <c r="M210" s="4" t="n"/>
-      <c r="N210" s="4" t="n"/>
+      <c r="N210" s="4" t="inlineStr">
+        <is>
+          <t>Veracruz, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -9732,7 +10568,11 @@
       <c r="K211" s="4" t="n"/>
       <c r="L211" s="4" t="n"/>
       <c r="M211" s="4" t="n"/>
-      <c r="N211" s="4" t="n"/>
+      <c r="N211" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising MXI-GU, MXI-RA, and MXI-RG.</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -9776,7 +10616,11 @@
       <c r="K212" s="4" t="n"/>
       <c r="L212" s="4" t="n"/>
       <c r="M212" s="4" t="n"/>
-      <c r="N212" s="4" t="n"/>
+      <c r="N212" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising MXN-BC, MXN-BS, MXN-SI, and MXN-SO.</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -9820,7 +10664,11 @@
       <c r="K213" s="4" t="n"/>
       <c r="L213" s="4" t="n"/>
       <c r="M213" s="4" t="n"/>
-      <c r="N213" s="4" t="n"/>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising MXS-CL, MXS-GR, MXS-JA, MXS-MI, MXS-NA, and MXS-OA.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -9864,7 +10712,11 @@
       <c r="K214" s="4" t="n"/>
       <c r="L214" s="4" t="n"/>
       <c r="M214" s="4" t="n"/>
-      <c r="N214" s="4" t="n"/>
+      <c r="N214" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising MXT-CA, MXT-CI, MXT-QR, MXT-TB, and MXT-YU.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -9908,7 +10760,11 @@
       <c r="K215" s="4" t="n"/>
       <c r="L215" s="4" t="n"/>
       <c r="M215" s="4" t="n"/>
-      <c r="N215" s="4" t="n"/>
+      <c r="N215" s="4" t="inlineStr">
+        <is>
+          <t>Myanmar (Burma)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -9952,7 +10808,11 @@
       <c r="K216" s="4" t="n"/>
       <c r="L216" s="4" t="n"/>
       <c r="M216" s="4" t="n"/>
-      <c r="N216" s="4" t="n"/>
+      <c r="N216" s="4" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -9996,7 +10856,11 @@
       <c r="K217" s="4" t="n"/>
       <c r="L217" s="4" t="n"/>
       <c r="M217" s="4" t="n"/>
-      <c r="N217" s="4" t="n"/>
+      <c r="N217" s="4" t="inlineStr">
+        <is>
+          <t>The South African province of KwaZulu-Natal</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -10040,7 +10904,11 @@
       <c r="K218" s="4" t="n"/>
       <c r="L218" s="4" t="n"/>
       <c r="M218" s="4" t="n"/>
-      <c r="N218" s="4" t="n"/>
+      <c r="N218" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of New Brunswick</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -10084,7 +10952,11 @@
       <c r="K219" s="4" t="n"/>
       <c r="L219" s="4" t="n"/>
       <c r="M219" s="4" t="n"/>
-      <c r="N219" s="4" t="n"/>
+      <c r="N219" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of North Carolina</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
@@ -10128,7 +11000,11 @@
       <c r="K220" s="4" t="n"/>
       <c r="L220" s="4" t="n"/>
       <c r="M220" s="4" t="n"/>
-      <c r="N220" s="4" t="n"/>
+      <c r="N220" s="4" t="inlineStr">
+        <is>
+          <t>The Nicobar Islands, India</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -10172,7 +11048,11 @@
       <c r="K221" s="4" t="n"/>
       <c r="L221" s="4" t="n"/>
       <c r="M221" s="4" t="n"/>
-      <c r="N221" s="4" t="n"/>
+      <c r="N221" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising NCS-CH, NCS-DA, NCS-IN, NCS-KB, NCS-KC, NCS-KR, NCS-SO, and NCS-ST.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
@@ -10216,7 +11096,11 @@
       <c r="K222" s="4" t="n"/>
       <c r="L222" s="4" t="n"/>
       <c r="M222" s="4" t="n"/>
-      <c r="N222" s="4" t="n"/>
+      <c r="N222" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of North Dakota</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
@@ -10260,7 +11144,11 @@
       <c r="K223" s="4" t="n"/>
       <c r="L223" s="4" t="n"/>
       <c r="M223" s="4" t="n"/>
-      <c r="N223" s="4" t="n"/>
+      <c r="N223" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Nebraska</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
@@ -10304,7 +11192,11 @@
       <c r="K224" s="4" t="n"/>
       <c r="L224" s="4" t="n"/>
       <c r="M224" s="4" t="n"/>
-      <c r="N224" s="4" t="n"/>
+      <c r="N224" s="4" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -10348,7 +11240,11 @@
       <c r="K225" s="4" t="n"/>
       <c r="L225" s="4" t="n"/>
       <c r="M225" s="4" t="n"/>
-      <c r="N225" s="4" t="n"/>
+      <c r="N225" s="4" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
@@ -10392,7 +11288,11 @@
       <c r="K226" s="4" t="n"/>
       <c r="L226" s="4" t="n"/>
       <c r="M226" s="4" t="n"/>
-      <c r="N226" s="4" t="n"/>
+      <c r="N226" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Nevada</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
@@ -10432,7 +11332,11 @@
       <c r="K227" s="4" t="n"/>
       <c r="L227" s="4" t="n"/>
       <c r="M227" s="4" t="n"/>
-      <c r="N227" s="4" t="n"/>
+      <c r="N227" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising NFK-LH and NFK-NI.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
@@ -10472,7 +11376,11 @@
       <c r="K228" s="4" t="n"/>
       <c r="L228" s="4" t="n"/>
       <c r="M228" s="4" t="n"/>
-      <c r="N228" s="4" t="n"/>
+      <c r="N228" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising NFL-NE and NFL-SP.</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
@@ -10516,7 +11424,11 @@
       <c r="K229" s="4" t="n"/>
       <c r="L229" s="4" t="n"/>
       <c r="M229" s="4" t="n"/>
-      <c r="N229" s="4" t="n"/>
+      <c r="N229" s="4" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
@@ -10560,7 +11472,11 @@
       <c r="K230" s="4" t="n"/>
       <c r="L230" s="4" t="n"/>
       <c r="M230" s="4" t="n"/>
-      <c r="N230" s="4" t="n"/>
+      <c r="N230" s="4" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
@@ -10604,7 +11520,11 @@
       <c r="K231" s="4" t="n"/>
       <c r="L231" s="4" t="n"/>
       <c r="M231" s="4" t="n"/>
-      <c r="N231" s="4" t="n"/>
+      <c r="N231" s="4" t="inlineStr">
+        <is>
+          <t>Nicaragua</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
@@ -10648,7 +11568,11 @@
         </is>
       </c>
       <c r="M232" s="4" t="n"/>
-      <c r="N232" s="4" t="n"/>
+      <c r="N232" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising NLA-BO and NLA-CU.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
@@ -10692,7 +11616,11 @@
       <c r="K233" s="4" t="n"/>
       <c r="L233" s="4" t="n"/>
       <c r="M233" s="4" t="n"/>
-      <c r="N233" s="4" t="n"/>
+      <c r="N233" s="4" t="inlineStr">
+        <is>
+          <t>The Nansei (Ryukyu) Islands, Japan</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
@@ -10736,7 +11664,11 @@
       <c r="K234" s="4" t="n"/>
       <c r="L234" s="4" t="n"/>
       <c r="M234" s="4" t="n"/>
-      <c r="N234" s="4" t="n"/>
+      <c r="N234" s="4" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -10780,7 +11712,11 @@
       <c r="K235" s="4" t="n"/>
       <c r="L235" s="4" t="n"/>
       <c r="M235" s="4" t="n"/>
-      <c r="N235" s="4" t="n"/>
+      <c r="N235" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising NPP-GA, NPP-LI, NPP-MP, and NPP-NW.</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
@@ -10824,7 +11760,11 @@
       <c r="K236" s="4" t="n"/>
       <c r="L236" s="4" t="n"/>
       <c r="M236" s="4" t="n"/>
-      <c r="N236" s="4" t="n"/>
+      <c r="N236" s="4" t="inlineStr">
+        <is>
+          <t>Naoero, an island country in the Pacific also long known as Nauru</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
@@ -10868,7 +11808,11 @@
       <c r="K237" s="4" t="n"/>
       <c r="L237" s="4" t="n"/>
       <c r="M237" s="4" t="n"/>
-      <c r="N237" s="4" t="n"/>
+      <c r="N237" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Nova Scotia</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
@@ -10912,7 +11856,11 @@
       <c r="K238" s="4" t="n"/>
       <c r="L238" s="4" t="n"/>
       <c r="M238" s="4" t="n"/>
-      <c r="N238" s="4" t="n"/>
+      <c r="N238" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising NSW-CT and NSW-NS.</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
@@ -10956,7 +11904,11 @@
       <c r="K239" s="4" t="n"/>
       <c r="L239" s="4" t="n"/>
       <c r="M239" s="4" t="n"/>
-      <c r="N239" s="4" t="n"/>
+      <c r="N239" s="4" t="inlineStr">
+        <is>
+          <t>The Northern Territory of Australia</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
@@ -11000,7 +11952,11 @@
       <c r="K240" s="4" t="n"/>
       <c r="L240" s="4" t="n"/>
       <c r="M240" s="4" t="n"/>
-      <c r="N240" s="4" t="n"/>
+      <c r="N240" s="4" t="inlineStr">
+        <is>
+          <t>Niue, Pacific island nation</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
@@ -11044,7 +12000,11 @@
       <c r="K241" s="4" t="n"/>
       <c r="L241" s="4" t="n"/>
       <c r="M241" s="4" t="n"/>
-      <c r="N241" s="4" t="n"/>
+      <c r="N241" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian territory of Nunavut</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
@@ -11100,7 +12060,11 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="N242" s="4" t="n"/>
+      <c r="N242" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising NWB-BH, NWB-CR, NWB-KO, NWB-MA, NWB-MN, NWB-SE, and NWB-SL.</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
@@ -11144,7 +12108,11 @@
       <c r="K243" s="4" t="n"/>
       <c r="L243" s="4" t="n"/>
       <c r="M243" s="4" t="n"/>
-      <c r="N243" s="4" t="n"/>
+      <c r="N243" s="4" t="inlineStr">
+        <is>
+          <t>New Caledonia, French territory in the Pacific</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
@@ -11184,7 +12152,11 @@
       <c r="K244" s="4" t="n"/>
       <c r="L244" s="4" t="n"/>
       <c r="M244" s="4" t="n"/>
-      <c r="N244" s="4" t="n"/>
+      <c r="N244" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising NWG-IJ and NWG-PN.</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
@@ -11228,7 +12200,11 @@
       <c r="K245" s="4" t="n"/>
       <c r="L245" s="4" t="n"/>
       <c r="M245" s="4" t="n"/>
-      <c r="N245" s="4" t="n"/>
+      <c r="N245" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of New Hampshire</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
@@ -11272,7 +12248,11 @@
       <c r="K246" s="4" t="n"/>
       <c r="L246" s="4" t="n"/>
       <c r="M246" s="4" t="n"/>
-      <c r="N246" s="4" t="n"/>
+      <c r="N246" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of New Jersey</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
@@ -11316,7 +12296,11 @@
       <c r="K247" s="4" t="n"/>
       <c r="L247" s="4" t="n"/>
       <c r="M247" s="4" t="n"/>
-      <c r="N247" s="4" t="n"/>
+      <c r="N247" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of New Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
@@ -11360,7 +12344,11 @@
       <c r="K248" s="4" t="n"/>
       <c r="L248" s="4" t="n"/>
       <c r="M248" s="4" t="n"/>
-      <c r="N248" s="4" t="n"/>
+      <c r="N248" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian territory of Northwest Territories</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
@@ -11404,7 +12392,11 @@
       <c r="K249" s="4" t="n"/>
       <c r="L249" s="4" t="n"/>
       <c r="M249" s="4" t="n"/>
-      <c r="N249" s="4" t="n"/>
+      <c r="N249" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of New York</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
@@ -11448,7 +12440,11 @@
       <c r="K250" s="4" t="n"/>
       <c r="L250" s="4" t="n"/>
       <c r="M250" s="4" t="n"/>
-      <c r="N250" s="4" t="n"/>
+      <c r="N250" s="4" t="inlineStr">
+        <is>
+          <t>North Island, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
@@ -11492,7 +12488,11 @@
       <c r="K251" s="4" t="n"/>
       <c r="L251" s="4" t="n"/>
       <c r="M251" s="4" t="n"/>
-      <c r="N251" s="4" t="n"/>
+      <c r="N251" s="4" t="inlineStr">
+        <is>
+          <t>South Island, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
@@ -11536,7 +12536,11 @@
       <c r="K252" s="4" t="n"/>
       <c r="L252" s="4" t="n"/>
       <c r="M252" s="4" t="n"/>
-      <c r="N252" s="4" t="n"/>
+      <c r="N252" s="4" t="inlineStr">
+        <is>
+          <t>The South African province of Free State</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
@@ -11580,7 +12584,11 @@
       <c r="K253" s="4" t="n"/>
       <c r="L253" s="4" t="n"/>
       <c r="M253" s="4" t="n"/>
-      <c r="N253" s="4" t="n"/>
+      <c r="N253" s="4" t="inlineStr">
+        <is>
+          <t>The Ogasawara (Bonin) Islands, Japan</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
@@ -11624,7 +12632,11 @@
       <c r="K254" s="4" t="n"/>
       <c r="L254" s="4" t="n"/>
       <c r="M254" s="4" t="n"/>
-      <c r="N254" s="4" t="n"/>
+      <c r="N254" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Ohio</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
@@ -11668,7 +12680,11 @@
       <c r="K255" s="4" t="n"/>
       <c r="L255" s="4" t="n"/>
       <c r="M255" s="4" t="n"/>
-      <c r="N255" s="4" t="n"/>
+      <c r="N255" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Oklahoma</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
@@ -11712,7 +12728,11 @@
       <c r="K256" s="4" t="n"/>
       <c r="L256" s="4" t="n"/>
       <c r="M256" s="4" t="n"/>
-      <c r="N256" s="4" t="n"/>
+      <c r="N256" s="4" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
@@ -11756,7 +12776,11 @@
       <c r="K257" s="4" t="n"/>
       <c r="L257" s="4" t="n"/>
       <c r="M257" s="4" t="n"/>
-      <c r="N257" s="4" t="n"/>
+      <c r="N257" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Ontario</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
@@ -11800,7 +12824,11 @@
       <c r="K258" s="4" t="n"/>
       <c r="L258" s="4" t="n"/>
       <c r="M258" s="4" t="n"/>
-      <c r="N258" s="4" t="n"/>
+      <c r="N258" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Oregon</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
@@ -11844,7 +12872,11 @@
       <c r="K259" s="4" t="n"/>
       <c r="L259" s="4" t="n"/>
       <c r="M259" s="4" t="n"/>
-      <c r="N259" s="4" t="n"/>
+      <c r="N259" s="4" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
@@ -11884,7 +12916,11 @@
       <c r="K260" s="4" t="n"/>
       <c r="L260" s="4" t="n"/>
       <c r="M260" s="4" t="n"/>
-      <c r="N260" s="4" t="n"/>
+      <c r="N260" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising PAL-GZ, PAL-IS, PAL-JO, and PAL-WB.</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
@@ -11928,7 +12964,11 @@
       <c r="K261" s="4" t="n"/>
       <c r="L261" s="4" t="n"/>
       <c r="M261" s="4" t="n"/>
-      <c r="N261" s="4" t="n"/>
+      <c r="N261" s="4" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
@@ -11972,7 +13012,11 @@
       <c r="K262" s="4" t="n"/>
       <c r="L262" s="4" t="n"/>
       <c r="M262" s="4" t="n"/>
-      <c r="N262" s="4" t="n"/>
+      <c r="N262" s="4" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
@@ -12016,7 +13060,11 @@
       <c r="K263" s="4" t="n"/>
       <c r="L263" s="4" t="n"/>
       <c r="M263" s="4" t="n"/>
-      <c r="N263" s="4" t="n"/>
+      <c r="N263" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Prince Edward Island</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
@@ -12060,7 +13108,11 @@
       <c r="K264" s="4" t="n"/>
       <c r="L264" s="4" t="n"/>
       <c r="M264" s="4" t="n"/>
-      <c r="N264" s="4" t="n"/>
+      <c r="N264" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Pennsylvania</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
@@ -12104,7 +13156,11 @@
       <c r="K265" s="4" t="n"/>
       <c r="L265" s="4" t="n"/>
       <c r="M265" s="4" t="n"/>
-      <c r="N265" s="4" t="n"/>
+      <c r="N265" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
@@ -12148,7 +13204,11 @@
       <c r="K266" s="4" t="n"/>
       <c r="L266" s="4" t="n"/>
       <c r="M266" s="4" t="n"/>
-      <c r="N266" s="4" t="n"/>
+      <c r="N266" s="4" t="inlineStr">
+        <is>
+          <t>The Philippines</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
@@ -12192,7 +13252,11 @@
       <c r="K267" s="4" t="n"/>
       <c r="L267" s="4" t="n"/>
       <c r="M267" s="4" t="n"/>
-      <c r="N267" s="4" t="n"/>
+      <c r="N267" s="4" t="inlineStr">
+        <is>
+          <t>The Phoenix Islands, Kiribati</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
@@ -12236,7 +13300,11 @@
       <c r="K268" s="4" t="n"/>
       <c r="L268" s="4" t="n"/>
       <c r="M268" s="4" t="n"/>
-      <c r="N268" s="4" t="n"/>
+      <c r="N268" s="4" t="inlineStr">
+        <is>
+          <t>The Pitcairn Islands</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
@@ -12280,7 +13348,11 @@
       <c r="K269" s="4" t="n"/>
       <c r="L269" s="4" t="n"/>
       <c r="M269" s="4" t="n"/>
-      <c r="N269" s="4" t="n"/>
+      <c r="N269" s="4" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
@@ -12324,7 +13396,11 @@
       <c r="K270" s="4" t="n"/>
       <c r="L270" s="4" t="n"/>
       <c r="M270" s="4" t="n"/>
-      <c r="N270" s="4" t="n"/>
+      <c r="N270" s="4" t="inlineStr">
+        <is>
+          <t>Continental Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
@@ -12368,7 +13444,11 @@
       <c r="K271" s="4" t="n"/>
       <c r="L271" s="4" t="n"/>
       <c r="M271" s="4" t="n"/>
-      <c r="N271" s="4" t="n"/>
+      <c r="N271" s="4" t="inlineStr">
+        <is>
+          <t>Primorye, Russian Far East (Primorsky Krai)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -12412,7 +13492,11 @@
       <c r="K272" s="4" t="n"/>
       <c r="L272" s="4" t="n"/>
       <c r="M272" s="4" t="n"/>
-      <c r="N272" s="4" t="n"/>
+      <c r="N272" s="4" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -12456,7 +13540,11 @@
       <c r="K273" s="4" t="n"/>
       <c r="L273" s="4" t="n"/>
       <c r="M273" s="4" t="n"/>
-      <c r="N273" s="4" t="n"/>
+      <c r="N273" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising QLD-CS and QLD-QU.</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
@@ -12500,7 +13588,11 @@
       <c r="K274" s="4" t="n"/>
       <c r="L274" s="4" t="n"/>
       <c r="M274" s="4" t="n"/>
-      <c r="N274" s="4" t="n"/>
+      <c r="N274" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Quebec</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -12544,7 +13636,11 @@
       <c r="K275" s="4" t="n"/>
       <c r="L275" s="4" t="n"/>
       <c r="M275" s="4" t="n"/>
-      <c r="N275" s="4" t="n"/>
+      <c r="N275" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising REU-RE and REU-TR.</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
@@ -12588,7 +13684,11 @@
       <c r="K276" s="4" t="n"/>
       <c r="L276" s="4" t="n"/>
       <c r="M276" s="4" t="n"/>
-      <c r="N276" s="4" t="n"/>
+      <c r="N276" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Rhode Island</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -12632,7 +13732,11 @@
       <c r="K277" s="4" t="n"/>
       <c r="L277" s="4" t="n"/>
       <c r="M277" s="4" t="n"/>
-      <c r="N277" s="4" t="n"/>
+      <c r="N277" s="4" t="inlineStr">
+        <is>
+          <t>Rodrigues Island, Mauritius</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
@@ -12676,7 +13780,11 @@
       <c r="K278" s="4" t="n"/>
       <c r="L278" s="4" t="n"/>
       <c r="M278" s="4" t="n"/>
-      <c r="N278" s="4" t="n"/>
+      <c r="N278" s="4" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -12720,7 +13828,11 @@
       <c r="K279" s="4" t="n"/>
       <c r="L279" s="4" t="n"/>
       <c r="M279" s="4" t="n"/>
-      <c r="N279" s="4" t="n"/>
+      <c r="N279" s="4" t="inlineStr">
+        <is>
+          <t>Central European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -12764,7 +13876,11 @@
       <c r="K280" s="4" t="n"/>
       <c r="L280" s="4" t="n"/>
       <c r="M280" s="4" t="n"/>
-      <c r="N280" s="4" t="n"/>
+      <c r="N280" s="4" t="inlineStr">
+        <is>
+          <t>East European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
@@ -12808,7 +13924,11 @@
       <c r="K281" s="4" t="n"/>
       <c r="L281" s="4" t="n"/>
       <c r="M281" s="4" t="n"/>
-      <c r="N281" s="4" t="n"/>
+      <c r="N281" s="4" t="inlineStr">
+        <is>
+          <t>North European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
@@ -12852,7 +13972,11 @@
       <c r="K282" s="4" t="n"/>
       <c r="L282" s="4" t="n"/>
       <c r="M282" s="4" t="n"/>
-      <c r="N282" s="4" t="n"/>
+      <c r="N282" s="4" t="inlineStr">
+        <is>
+          <t>South European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -12896,7 +14020,11 @@
       <c r="K283" s="4" t="n"/>
       <c r="L283" s="4" t="n"/>
       <c r="M283" s="4" t="n"/>
-      <c r="N283" s="4" t="n"/>
+      <c r="N283" s="4" t="inlineStr">
+        <is>
+          <t>Northwest European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
@@ -12940,7 +14068,11 @@
       <c r="K284" s="4" t="n"/>
       <c r="L284" s="4" t="n"/>
       <c r="M284" s="4" t="n"/>
-      <c r="N284" s="4" t="n"/>
+      <c r="N284" s="4" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
@@ -12984,7 +14116,11 @@
       <c r="K285" s="4" t="n"/>
       <c r="L285" s="4" t="n"/>
       <c r="M285" s="4" t="n"/>
-      <c r="N285" s="4" t="n"/>
+      <c r="N285" s="4" t="inlineStr">
+        <is>
+          <t>Sakhalin Island, Russian Far East</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
@@ -13024,7 +14160,11 @@
       <c r="K286" s="4" t="n"/>
       <c r="L286" s="4" t="n"/>
       <c r="M286" s="4" t="n"/>
-      <c r="N286" s="4" t="n"/>
+      <c r="N286" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising SAM-AS and SAM-WS.</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
@@ -13068,7 +14208,11 @@
       <c r="K287" s="4" t="n"/>
       <c r="L287" s="4" t="n"/>
       <c r="M287" s="4" t="n"/>
-      <c r="N287" s="4" t="n"/>
+      <c r="N287" s="4" t="inlineStr">
+        <is>
+          <t>Sardinia, Italy</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
@@ -13112,7 +14256,11 @@
       <c r="K288" s="4" t="n"/>
       <c r="L288" s="4" t="n"/>
       <c r="M288" s="4" t="n"/>
-      <c r="N288" s="4" t="n"/>
+      <c r="N288" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Saskatchewan</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
@@ -13156,7 +14304,11 @@
       <c r="K289" s="4" t="n"/>
       <c r="L289" s="4" t="n"/>
       <c r="M289" s="4" t="n"/>
-      <c r="N289" s="4" t="n"/>
+      <c r="N289" s="4" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
@@ -13200,7 +14352,11 @@
       <c r="K290" s="4" t="n"/>
       <c r="L290" s="4" t="n"/>
       <c r="M290" s="4" t="n"/>
-      <c r="N290" s="4" t="n"/>
+      <c r="N290" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of South Carolina</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
@@ -13244,7 +14400,11 @@
       <c r="K291" s="4" t="n"/>
       <c r="L291" s="4" t="n"/>
       <c r="M291" s="4" t="n"/>
-      <c r="N291" s="4" t="n"/>
+      <c r="N291" s="4" t="inlineStr">
+        <is>
+          <t>The Society Islands, French Polynesia</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
@@ -13284,7 +14444,11 @@
       <c r="K292" s="4" t="n"/>
       <c r="L292" s="4" t="n"/>
       <c r="M292" s="4" t="n"/>
-      <c r="N292" s="4" t="n"/>
+      <c r="N292" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising SCS-PI and SCS-SI.</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
@@ -13328,7 +14492,11 @@
       <c r="K293" s="4" t="n"/>
       <c r="L293" s="4" t="n"/>
       <c r="M293" s="4" t="n"/>
-      <c r="N293" s="4" t="n"/>
+      <c r="N293" s="4" t="inlineStr">
+        <is>
+          <t>The Santa Cruz Islands, Solomon Islands</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
@@ -13372,7 +14540,11 @@
       <c r="K294" s="4" t="n"/>
       <c r="L294" s="4" t="n"/>
       <c r="M294" s="4" t="n"/>
-      <c r="N294" s="4" t="n"/>
+      <c r="N294" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of South Dakota</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
@@ -13416,7 +14588,11 @@
       <c r="K295" s="4" t="n"/>
       <c r="L295" s="4" t="n"/>
       <c r="M295" s="4" t="n"/>
-      <c r="N295" s="4" t="n"/>
+      <c r="N295" s="4" t="inlineStr">
+        <is>
+          <t>The Selvagens Islands, Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
@@ -13460,7 +14636,11 @@
       <c r="K296" s="4" t="n"/>
       <c r="L296" s="4" t="n"/>
       <c r="M296" s="4" t="n"/>
-      <c r="N296" s="4" t="n"/>
+      <c r="N296" s="4" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
@@ -13504,7 +14684,11 @@
       <c r="K297" s="4" t="n"/>
       <c r="L297" s="4" t="n"/>
       <c r="M297" s="4" t="n"/>
-      <c r="N297" s="4" t="n"/>
+      <c r="N297" s="4" t="inlineStr">
+        <is>
+          <t>Seychelles</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
@@ -13548,7 +14732,11 @@
       <c r="K298" s="4" t="n"/>
       <c r="L298" s="4" t="n"/>
       <c r="M298" s="4" t="n"/>
-      <c r="N298" s="4" t="n"/>
+      <c r="N298" s="4" t="inlineStr">
+        <is>
+          <t>South Georgia Island</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
@@ -13588,7 +14776,11 @@
       <c r="K299" s="4" t="n"/>
       <c r="L299" s="4" t="n"/>
       <c r="M299" s="4" t="n"/>
-      <c r="N299" s="4" t="n"/>
+      <c r="N299" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising SIC-MA and SIC-SI.</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
@@ -13632,7 +14824,11 @@
       <c r="K300" s="4" t="n"/>
       <c r="L300" s="4" t="n"/>
       <c r="M300" s="4" t="n"/>
-      <c r="N300" s="4" t="n"/>
+      <c r="N300" s="4" t="inlineStr">
+        <is>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
@@ -13676,7 +14872,11 @@
       <c r="K301" s="4" t="n"/>
       <c r="L301" s="4" t="n"/>
       <c r="M301" s="4" t="n"/>
-      <c r="N301" s="4" t="n"/>
+      <c r="N301" s="4" t="inlineStr">
+        <is>
+          <t>The Sinai Peninsula, Egypt</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
@@ -13720,7 +14920,11 @@
       <c r="K302" s="4" t="n"/>
       <c r="L302" s="4" t="n"/>
       <c r="M302" s="4" t="n"/>
-      <c r="N302" s="4" t="n"/>
+      <c r="N302" s="4" t="inlineStr">
+        <is>
+          <t>The Australian state of South Australia</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -13764,7 +14968,11 @@
       <c r="K303" s="4" t="n"/>
       <c r="L303" s="4" t="n"/>
       <c r="M303" s="4" t="n"/>
-      <c r="N303" s="4" t="n"/>
+      <c r="N303" s="4" t="inlineStr">
+        <is>
+          <t>Socotra Island, Yemen</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
@@ -13804,7 +15012,11 @@
       <c r="K304" s="4" t="n"/>
       <c r="L304" s="4" t="n"/>
       <c r="M304" s="4" t="n"/>
-      <c r="N304" s="4" t="n"/>
+      <c r="N304" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising SOL-NO and SOL-SO.</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -13848,7 +15060,11 @@
       <c r="K305" s="4" t="n"/>
       <c r="L305" s="4" t="n"/>
       <c r="M305" s="4" t="n"/>
-      <c r="N305" s="4" t="n"/>
+      <c r="N305" s="4" t="inlineStr">
+        <is>
+          <t>Somalia</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
@@ -13888,7 +15104,11 @@
       <c r="K306" s="4" t="n"/>
       <c r="L306" s="4" t="n"/>
       <c r="M306" s="4" t="n"/>
-      <c r="N306" s="4" t="n"/>
+      <c r="N306" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising SPA-AN, SPA-GI, and SPA-SP.</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -13932,7 +15152,11 @@
       <c r="K307" s="4" t="n"/>
       <c r="L307" s="4" t="n"/>
       <c r="M307" s="4" t="n"/>
-      <c r="N307" s="4" t="n"/>
+      <c r="N307" s="4" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
@@ -13976,7 +15200,11 @@
       <c r="K308" s="4" t="n"/>
       <c r="L308" s="4" t="n"/>
       <c r="M308" s="4" t="n"/>
-      <c r="N308" s="4" t="n"/>
+      <c r="N308" s="4" t="inlineStr">
+        <is>
+          <t>The South Sandwich Islands</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
@@ -14020,7 +15248,11 @@
       <c r="K309" s="4" t="n"/>
       <c r="L309" s="4" t="n"/>
       <c r="M309" s="4" t="n"/>
-      <c r="N309" s="4" t="n"/>
+      <c r="N309" s="4" t="inlineStr">
+        <is>
+          <t>Saint Helena Island</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
@@ -14060,7 +15292,11 @@
       <c r="K310" s="4" t="n"/>
       <c r="L310" s="4" t="n"/>
       <c r="M310" s="4" t="n"/>
-      <c r="N310" s="4" t="n"/>
+      <c r="N310" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising SUD-SD and SUD-SS.</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
@@ -14104,7 +15340,11 @@
       <c r="K311" s="4" t="n"/>
       <c r="L311" s="4" t="n"/>
       <c r="M311" s="4" t="n"/>
-      <c r="N311" s="4" t="n"/>
+      <c r="N311" s="4" t="inlineStr">
+        <is>
+          <t>Sulawesi, Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
@@ -14148,7 +15388,11 @@
       <c r="K312" s="4" t="n"/>
       <c r="L312" s="4" t="n"/>
       <c r="M312" s="4" t="n"/>
-      <c r="N312" s="4" t="n"/>
+      <c r="N312" s="4" t="inlineStr">
+        <is>
+          <t>Sumatra, Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -14192,7 +15436,11 @@
       <c r="K313" s="4" t="n"/>
       <c r="L313" s="4" t="n"/>
       <c r="M313" s="4" t="n"/>
-      <c r="N313" s="4" t="n"/>
+      <c r="N313" s="4" t="inlineStr">
+        <is>
+          <t>Suriname</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
@@ -14236,7 +15484,11 @@
       <c r="K314" s="4" t="n"/>
       <c r="L314" s="4" t="n"/>
       <c r="M314" s="4" t="n"/>
-      <c r="N314" s="4" t="n"/>
+      <c r="N314" s="4" t="inlineStr">
+        <is>
+          <t>Svalbard, Norway</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -14276,7 +15528,11 @@
       <c r="K315" s="4" t="n"/>
       <c r="L315" s="4" t="n"/>
       <c r="M315" s="4" t="n"/>
-      <c r="N315" s="4" t="n"/>
+      <c r="N315" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising SWC-CC, SWC-HC, and SWC-NC.</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
@@ -14320,7 +15576,11 @@
       <c r="K316" s="4" t="n"/>
       <c r="L316" s="4" t="n"/>
       <c r="M316" s="4" t="n"/>
-      <c r="N316" s="4" t="n"/>
+      <c r="N316" s="4" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -14364,7 +15624,11 @@
       <c r="K317" s="4" t="n"/>
       <c r="L317" s="4" t="n"/>
       <c r="M317" s="4" t="n"/>
-      <c r="N317" s="4" t="n"/>
+      <c r="N317" s="4" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
@@ -14408,7 +15672,11 @@
       <c r="K318" s="4" t="n"/>
       <c r="L318" s="4" t="n"/>
       <c r="M318" s="4" t="n"/>
-      <c r="N318" s="4" t="n"/>
+      <c r="N318" s="4" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -14452,7 +15720,11 @@
       <c r="K319" s="4" t="n"/>
       <c r="L319" s="4" t="n"/>
       <c r="M319" s="4" t="n"/>
-      <c r="N319" s="4" t="n"/>
+      <c r="N319" s="4" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
@@ -14496,7 +15768,11 @@
       <c r="K320" s="4" t="n"/>
       <c r="L320" s="4" t="n"/>
       <c r="M320" s="4" t="n"/>
-      <c r="N320" s="4" t="n"/>
+      <c r="N320" s="4" t="inlineStr">
+        <is>
+          <t>The Australian state of Tasmania</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -14540,7 +15816,11 @@
       <c r="K321" s="4" t="n"/>
       <c r="L321" s="4" t="n"/>
       <c r="M321" s="4" t="n"/>
-      <c r="N321" s="4" t="n"/>
+      <c r="N321" s="4" t="inlineStr">
+        <is>
+          <t>The Turks and Caicos Islands</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -14588,7 +15868,11 @@
           <t>#5</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n"/>
+      <c r="N322" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising TCS-AB, TCS-AD, TCS-AR, TCS-AZ, TCS-GR, TCS-NA, and TCS-NK.</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -14632,7 +15916,11 @@
       <c r="K323" s="4" t="n"/>
       <c r="L323" s="4" t="n"/>
       <c r="M323" s="4" t="n"/>
-      <c r="N323" s="4" t="n"/>
+      <c r="N323" s="4" t="inlineStr">
+        <is>
+          <t>Tristan da Cunha, a remote island group in the South Atlantic</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
@@ -14676,7 +15964,11 @@
       <c r="K324" s="4" t="n"/>
       <c r="L324" s="4" t="n"/>
       <c r="M324" s="4" t="n"/>
-      <c r="N324" s="4" t="n"/>
+      <c r="N324" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Tennessee</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -14720,7 +16012,11 @@
       <c r="K325" s="4" t="n"/>
       <c r="L325" s="4" t="n"/>
       <c r="M325" s="4" t="n"/>
-      <c r="N325" s="4" t="n"/>
+      <c r="N325" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Texas</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
@@ -14764,7 +16060,11 @@
       <c r="K326" s="4" t="n"/>
       <c r="L326" s="4" t="n"/>
       <c r="M326" s="4" t="n"/>
-      <c r="N326" s="4" t="n"/>
+      <c r="N326" s="4" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -14808,7 +16108,11 @@
       <c r="K327" s="4" t="n"/>
       <c r="L327" s="4" t="n"/>
       <c r="M327" s="4" t="n"/>
-      <c r="N327" s="4" t="n"/>
+      <c r="N327" s="4" t="inlineStr">
+        <is>
+          <t>Turkmenistan</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
@@ -14852,7 +16156,11 @@
       <c r="K328" s="4" t="n"/>
       <c r="L328" s="4" t="n"/>
       <c r="M328" s="4" t="n"/>
-      <c r="N328" s="4" t="n"/>
+      <c r="N328" s="4" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
@@ -14892,7 +16200,11 @@
       <c r="K329" s="4" t="n"/>
       <c r="L329" s="4" t="n"/>
       <c r="M329" s="4" t="n"/>
-      <c r="N329" s="4" t="n"/>
+      <c r="N329" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising TOK-MA, TOK-SW, and TOK-TO.</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
@@ -14936,7 +16248,11 @@
       <c r="K330" s="4" t="n"/>
       <c r="L330" s="4" t="n"/>
       <c r="M330" s="4" t="n"/>
-      <c r="N330" s="4" t="n"/>
+      <c r="N330" s="4" t="inlineStr">
+        <is>
+          <t>Tonga</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
@@ -14980,7 +16296,11 @@
       <c r="K331" s="4" t="n"/>
       <c r="L331" s="4" t="n"/>
       <c r="M331" s="4" t="n"/>
-      <c r="N331" s="4" t="n"/>
+      <c r="N331" s="4" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
@@ -15024,7 +16344,11 @@
       <c r="K332" s="4" t="n"/>
       <c r="L332" s="4" t="n"/>
       <c r="M332" s="4" t="n"/>
-      <c r="N332" s="4" t="n"/>
+      <c r="N332" s="4" t="inlineStr">
+        <is>
+          <t>The Tuamotu Archipelago, French Polynesia</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
@@ -15068,7 +16392,11 @@
       <c r="K333" s="4" t="n"/>
       <c r="L333" s="4" t="n"/>
       <c r="M333" s="4" t="n"/>
-      <c r="N333" s="4" t="n"/>
+      <c r="N333" s="4" t="inlineStr">
+        <is>
+          <t>The Tubuai (Austral) Islands, French Polynesia</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
@@ -15124,7 +16452,11 @@
           <t>#22</t>
         </is>
       </c>
-      <c r="N334" s="4" t="n"/>
+      <c r="N334" s="4" t="inlineStr">
+        <is>
+          <t>European Turkey (Eastern Thrace)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -15168,7 +16500,11 @@
       <c r="K335" s="4" t="n"/>
       <c r="L335" s="4" t="n"/>
       <c r="M335" s="4" t="n"/>
-      <c r="N335" s="4" t="n"/>
+      <c r="N335" s="4" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
@@ -15224,7 +16560,11 @@
           <t>#22</t>
         </is>
       </c>
-      <c r="N336" s="4" t="n"/>
+      <c r="N336" s="4" t="inlineStr">
+        <is>
+          <t>Turkey (Anatolia), the Asian part of the country</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
@@ -15268,7 +16608,11 @@
       <c r="K337" s="4" t="n"/>
       <c r="L337" s="4" t="n"/>
       <c r="M337" s="4" t="n"/>
-      <c r="N337" s="4" t="n"/>
+      <c r="N337" s="4" t="inlineStr">
+        <is>
+          <t>Tuvalu</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
@@ -15312,7 +16656,11 @@
       <c r="K338" s="4" t="n"/>
       <c r="L338" s="4" t="n"/>
       <c r="M338" s="4" t="n"/>
-      <c r="N338" s="4" t="n"/>
+      <c r="N338" s="4" t="inlineStr">
+        <is>
+          <t>The Tuva Republic, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
@@ -15356,7 +16704,11 @@
       <c r="K339" s="4" t="n"/>
       <c r="L339" s="4" t="n"/>
       <c r="M339" s="4" t="n"/>
-      <c r="N339" s="4" t="n"/>
+      <c r="N339" s="4" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
@@ -15400,7 +16752,11 @@
       <c r="K340" s="4" t="n"/>
       <c r="L340" s="4" t="n"/>
       <c r="M340" s="4" t="n"/>
-      <c r="N340" s="4" t="n"/>
+      <c r="N340" s="4" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
@@ -15440,7 +16796,11 @@
       <c r="K341" s="4" t="n"/>
       <c r="L341" s="4" t="n"/>
       <c r="M341" s="4" t="n"/>
-      <c r="N341" s="4" t="n"/>
+      <c r="N341" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising UKR-MO and UKR-UK.</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
@@ -15484,7 +16844,11 @@
       <c r="K342" s="4" t="n"/>
       <c r="L342" s="4" t="n"/>
       <c r="M342" s="4" t="n"/>
-      <c r="N342" s="4" t="n"/>
+      <c r="N342" s="4" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
@@ -15528,7 +16892,11 @@
       <c r="K343" s="4" t="n"/>
       <c r="L343" s="4" t="n"/>
       <c r="M343" s="4" t="n"/>
-      <c r="N343" s="4" t="n"/>
+      <c r="N343" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Utah</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
@@ -15572,7 +16940,11 @@
       <c r="K344" s="4" t="n"/>
       <c r="L344" s="4" t="n"/>
       <c r="M344" s="4" t="n"/>
-      <c r="N344" s="4" t="n"/>
+      <c r="N344" s="4" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
@@ -15616,7 +16988,11 @@
       <c r="K345" s="4" t="n"/>
       <c r="L345" s="4" t="n"/>
       <c r="M345" s="4" t="n"/>
-      <c r="N345" s="4" t="n"/>
+      <c r="N345" s="4" t="inlineStr">
+        <is>
+          <t>Vanuatu</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
@@ -15660,7 +17036,11 @@
       <c r="K346" s="4" t="n"/>
       <c r="L346" s="4" t="n"/>
       <c r="M346" s="4" t="n"/>
-      <c r="N346" s="4" t="n"/>
+      <c r="N346" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
@@ -15704,7 +17084,11 @@
       <c r="K347" s="4" t="n"/>
       <c r="L347" s="4" t="n"/>
       <c r="M347" s="4" t="n"/>
-      <c r="N347" s="4" t="n"/>
+      <c r="N347" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Vermont</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
@@ -15748,7 +17132,11 @@
       <c r="K348" s="4" t="n"/>
       <c r="L348" s="4" t="n"/>
       <c r="M348" s="4" t="n"/>
-      <c r="N348" s="4" t="n"/>
+      <c r="N348" s="4" t="inlineStr">
+        <is>
+          <t>The Australian state of Victoria</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
@@ -15792,7 +17180,11 @@
       <c r="K349" s="4" t="n"/>
       <c r="L349" s="4" t="n"/>
       <c r="M349" s="4" t="n"/>
-      <c r="N349" s="4" t="n"/>
+      <c r="N349" s="4" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
@@ -15836,7 +17228,11 @@
       <c r="K350" s="4" t="n"/>
       <c r="L350" s="4" t="n"/>
       <c r="M350" s="4" t="n"/>
-      <c r="N350" s="4" t="n"/>
+      <c r="N350" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela's offshore Caribbean islands (e.g. Margarita, Los Roques)</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
@@ -15880,7 +17276,11 @@
       <c r="K351" s="4" t="n"/>
       <c r="L351" s="4" t="n"/>
       <c r="M351" s="4" t="n"/>
-      <c r="N351" s="4" t="n"/>
+      <c r="N351" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Virginia</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
@@ -15924,7 +17324,11 @@
       <c r="K352" s="4" t="n"/>
       <c r="L352" s="4" t="n"/>
       <c r="M352" s="4" t="n"/>
-      <c r="N352" s="4" t="n"/>
+      <c r="N352" s="4" t="inlineStr">
+        <is>
+          <t>Wake Island, a U.S. territory in the Pacific</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
@@ -15968,7 +17372,11 @@
       <c r="K353" s="4" t="n"/>
       <c r="L353" s="4" t="n"/>
       <c r="M353" s="4" t="n"/>
-      <c r="N353" s="4" t="n"/>
+      <c r="N353" s="4" t="inlineStr">
+        <is>
+          <t>Wallis and Futuna, a French territory in the Pacific</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
@@ -16012,7 +17420,11 @@
       <c r="K354" s="4" t="n"/>
       <c r="L354" s="4" t="n"/>
       <c r="M354" s="4" t="n"/>
-      <c r="N354" s="4" t="n"/>
+      <c r="N354" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Washington</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
@@ -16056,7 +17468,11 @@
       <c r="K355" s="4" t="n"/>
       <c r="L355" s="4" t="n"/>
       <c r="M355" s="4" t="n"/>
-      <c r="N355" s="4" t="n"/>
+      <c r="N355" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising WAU-AC and WAU-WA.</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
@@ -16100,7 +17516,11 @@
       <c r="K356" s="4" t="n"/>
       <c r="L356" s="4" t="n"/>
       <c r="M356" s="4" t="n"/>
-      <c r="N356" s="4" t="n"/>
+      <c r="N356" s="4" t="inlineStr">
+        <is>
+          <t>Washington, D.C., USA</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
@@ -16136,7 +17556,11 @@
       <c r="K357" s="4" t="n"/>
       <c r="L357" s="4" t="n"/>
       <c r="M357" s="4" t="n"/>
-      <c r="N357" s="4" t="n"/>
+      <c r="N357" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising WHM-HP, WHM-JK, and WHM-UT.</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
@@ -16176,7 +17600,11 @@
       <c r="K358" s="4" t="n"/>
       <c r="L358" s="4" t="n"/>
       <c r="M358" s="4" t="n"/>
-      <c r="N358" s="4" t="n"/>
+      <c r="N358" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising WIN-BA, WIN-DO, WIN-GR, WIN-MA, WIN-SL, and WIN-SV.</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
@@ -16220,7 +17648,11 @@
       <c r="K359" s="4" t="n"/>
       <c r="L359" s="4" t="n"/>
       <c r="M359" s="4" t="n"/>
-      <c r="N359" s="4" t="n"/>
+      <c r="N359" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Wisconsin</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
@@ -16264,7 +17696,11 @@
       <c r="K360" s="4" t="n"/>
       <c r="L360" s="4" t="n"/>
       <c r="M360" s="4" t="n"/>
-      <c r="N360" s="4" t="n"/>
+      <c r="N360" s="4" t="inlineStr">
+        <is>
+          <t>Western Sahara, a disputed territory in North Africa</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
@@ -16308,7 +17744,11 @@
       <c r="K361" s="4" t="n"/>
       <c r="L361" s="4" t="n"/>
       <c r="M361" s="4" t="n"/>
-      <c r="N361" s="4" t="n"/>
+      <c r="N361" s="4" t="inlineStr">
+        <is>
+          <t>West Siberia, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
@@ -16352,7 +17792,11 @@
       <c r="K362" s="4" t="n"/>
       <c r="L362" s="4" t="n"/>
       <c r="M362" s="4" t="n"/>
-      <c r="N362" s="4" t="n"/>
+      <c r="N362" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of West Virginia</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
@@ -16396,7 +17840,11 @@
       <c r="K363" s="4" t="n"/>
       <c r="L363" s="4" t="n"/>
       <c r="M363" s="4" t="n"/>
-      <c r="N363" s="4" t="n"/>
+      <c r="N363" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Wyoming</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
@@ -16440,7 +17888,11 @@
       <c r="K364" s="4" t="n"/>
       <c r="L364" s="4" t="n"/>
       <c r="M364" s="4" t="n"/>
-      <c r="N364" s="4" t="n"/>
+      <c r="N364" s="4" t="inlineStr">
+        <is>
+          <t>Christmas Island, an Australian territory in the Indian Ocean</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
@@ -16484,7 +17936,11 @@
       <c r="K365" s="4" t="n"/>
       <c r="L365" s="4" t="n"/>
       <c r="M365" s="4" t="n"/>
-      <c r="N365" s="4" t="n"/>
+      <c r="N365" s="4" t="inlineStr">
+        <is>
+          <t>The Sakha Republic (Yakutia), Russia</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
@@ -16528,7 +17984,11 @@
       <c r="K366" s="4" t="n"/>
       <c r="L366" s="4" t="n"/>
       <c r="M366" s="4" t="n"/>
-      <c r="N366" s="4" t="n"/>
+      <c r="N366" s="4" t="inlineStr">
+        <is>
+          <t>The territory comprising YEM-NY and YEM-SY.</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
@@ -16572,7 +18032,11 @@
       <c r="K367" s="4" t="n"/>
       <c r="L367" s="4" t="n"/>
       <c r="M367" s="4" t="n"/>
-      <c r="N367" s="4" t="n"/>
+      <c r="N367" s="4" t="inlineStr">
+        <is>
+          <t>Yukon, a Canadian territory</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
@@ -16628,7 +18092,11 @@
           <t>#17</t>
         </is>
       </c>
-      <c r="N368" s="4" t="n"/>
+      <c r="N368" s="4" t="inlineStr">
+        <is>
+          <t>The Democratic Republic of the Congo</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
@@ -16672,7 +18140,11 @@
       <c r="K369" s="4" t="n"/>
       <c r="L369" s="4" t="n"/>
       <c r="M369" s="4" t="n"/>
-      <c r="N369" s="4" t="n"/>
+      <c r="N369" s="4" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
@@ -16716,7 +18188,11 @@
       <c r="K370" s="4" t="n"/>
       <c r="L370" s="4" t="n"/>
       <c r="M370" s="4" t="n"/>
-      <c r="N370" s="4" t="n"/>
+      <c r="N370" s="4" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
